--- a/陕西现货市场每日出清价格跟踪_2025至今_含风光分项.xlsx
+++ b/陕西现货市场每日出清价格跟踪_2025至今_含风光分项.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R7ae3ae9dd9944124"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据" sheetId="2" r:id="Rc546d115b95d41ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光分项" sheetId="3" r:id="R38cbfd6c81974565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="4" r:id="R995ac29fbd234ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光月度" sheetId="5" r:id="R05ed22801bdb40a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量" sheetId="6" r:id="R94fe6666ccef4aa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与跟踪计划" sheetId="7" r:id="Rfd7cddb3713d4d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R139c1d6da9fc40a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据" sheetId="2" r:id="R0962fd1e36764d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光分项" sheetId="3" r:id="R584b4fd2fb3047d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="4" r:id="Ra3f8ce54f72e4392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光月度" sheetId="5" r:id="Rf013e8672d0f4814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量" sheetId="6" r:id="Rdd1a46fa2f4e4177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与跟踪计划" sheetId="7" r:id="Ra721e50686c140b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={6AA75914-775E-1258-26BF-31C32F78C183}</x:author>
+    <x:author>tc={4EB2F4DF-DAD8-472D-A83B-66D96CC6C9BE}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -25,7 +25,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    2026-08-23网站当前回溯值；抓取于2026-08-26。公众号同日快报用于核验，差异不覆盖网站主序列。</x:t>
+    2026-08-29网站当前回溯值；抓取于2026-08-31。公众号同日快报用于核验，差异不覆盖网站主序列。</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -36,7 +36,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={18762616-B5C9-A5A2-3702-73E118E8E8DF}</x:author>
+    <x:author>tc={33BE459F-1A32-4F11-B54B-827CA68F48FA}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="C6" authorId="0">
@@ -961,7 +961,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc44a95ced0c04f38"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R968e07ba04594d22"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R70acb385c86b46e1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a726424902340ad"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1026,7 +1026,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7066577476594c60"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b1a95430feb4cf6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{1E964012-94A0-40D6-9A9D-2E850CA32C0B}"/>
+  <xltc:person displayName="User" id="{44D13FE9-BE9F-430D-872C-E424BA039A0E}"/>
 </xltc:personList>
 </file>
 
@@ -1234,15 +1234,15 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-25T23:03:38.642" personId="{1E964012-94A0-40D6-9A9D-2E850CA32C0B}" id="{6AA75914-775E-1258-26BF-31C32F78C183}">
-    <xltc:text>2026-08-23网站当前回溯值；抓取于2026-08-26。公众号同日快报用于核验，差异不覆盖网站主序列。</xltc:text>
+  <xltc:threadedComment ref="B18" dT="2026-08-31T02:36:40.616" personId="{44D13FE9-BE9F-430D-872C-E424BA039A0E}" id="{4EB2F4DF-DAD8-472D-A83B-66D96CC6C9BE}">
+    <xltc:text>2026-08-29网站当前回溯值；抓取于2026-08-31。公众号同日快报用于核验，差异不覆盖网站主序列。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
 
 <file path=xl/threadedcomments/threadedcomment2.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="C6" dT="2026-08-25T23:03:38.642" personId="{1E964012-94A0-40D6-9A9D-2E850CA32C0B}" id="{18762616-B5C9-A5A2-3702-73E118E8E8DF}">
+  <xltc:threadedComment ref="C6" dT="2026-08-31T02:36:40.616" personId="{44D13FE9-BE9F-430D-872C-E424BA039A0E}" id="{33BE459F-1A32-4F11-B54B-827CA68F48FA}">
     <xltc:text>主数据来自陕西电力交易中心现货专区公开接口；工作簿内保留网页入口便于人工复核。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1290,28 +1290,28 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="D2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="E2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="F2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="G2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="H2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-24｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1355,8 +1355,8 @@
         <x:v>完整日期数</x:v>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTA('每日数据'!$A$2:$A$602)</x:f>
-        <x:v>601</x:v>
+        <x:f>COUNTA('每日数据'!$A$2:$A$607)</x:f>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="C5" s="29"/>
       <x:c r="D5" s="29"/>
@@ -1370,8 +1370,8 @@
         <x:v>最新完整披露日</x:v>
       </x:c>
       <x:c r="B6" s="33" t="n">
-        <x:f>MAX('每日数据'!$A$2:$A$602)</x:f>
-        <x:v>46258</x:v>
+        <x:f>MAX('每日数据'!$A$2:$A$607)</x:f>
+        <x:v>46263</x:v>
       </x:c>
       <x:c r="C6" s="29"/>
       <x:c r="D6" s="29"/>
@@ -1385,8 +1385,8 @@
         <x:v>最新日前 / 实时均价</x:v>
       </x:c>
       <x:c r="B7" s="32" t="str">
-        <x:f>INDEX('每日数据'!$B$2:$B$602,MATCH(B6,'每日数据'!$A$2:$A$602,0))&amp;" / "&amp;INDEX('每日数据'!$C$2:$C$602,MATCH(B6,'每日数据'!$A$2:$A$602,0))</x:f>
-        <x:v>299.64 / 388.07</x:v>
+        <x:f>INDEX('每日数据'!$B$2:$B$607,MATCH(B6,'每日数据'!$A$2:$A$607,0))&amp;" / "&amp;INDEX('每日数据'!$C$2:$C$607,MATCH(B6,'每日数据'!$A$2:$A$607,0))</x:f>
+        <x:v>172.48 / 188.04</x:v>
       </x:c>
       <x:c r="C7" s="29"/>
       <x:c r="D7" s="29"/>
@@ -1549,28 +1549,28 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="B16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="C16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="D16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="E16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="F16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="G16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
       <x:c r="H16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-23）</x:v>
+        <x:v>口径差异示例（2026-08-29）</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -1598,16 +1598,16 @@
         <x:v>网站当前回溯接口</x:v>
       </x:c>
       <x:c r="B18" s="37" t="n">
-        <x:v>412.41</x:v>
+        <x:v>172.48</x:v>
       </x:c>
       <x:c r="C18" s="37" t="n">
-        <x:v>489.7</x:v>
+        <x:v>188.04</x:v>
       </x:c>
       <x:c r="D18" s="37" t="n">
-        <x:v>247.80957599999996</x:v>
+        <x:v>213.816904</x:v>
       </x:c>
       <x:c r="E18" s="37" t="n">
-        <x:v>260.024429</x:v>
+        <x:v>216.09009500000002</x:v>
       </x:c>
       <x:c r="F18" s="29"/>
       <x:c r="G18" s="29"/>
@@ -1618,16 +1618,16 @@
         <x:v>公众号次日日报</x:v>
       </x:c>
       <x:c r="B19" s="37" t="n">
-        <x:v>412.41</x:v>
+        <x:v>172.48</x:v>
       </x:c>
       <x:c r="C19" s="37" t="n">
-        <x:v>489.7</x:v>
+        <x:v>188.04</x:v>
       </x:c>
       <x:c r="D19" s="37" t="n">
-        <x:v>62</x:v>
+        <x:v>53.5</x:v>
       </x:c>
       <x:c r="E19" s="37" t="n">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F19" s="29"/>
       <x:c r="G19" s="29"/>
@@ -1820,7 +1820,7 @@
     <x:mergeCell ref="A24:H24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49fea70ca63a410c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R210b7f5b496d49b8"/>
 </x:worksheet>
 </file>
 
@@ -1932,7 +1932,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N2" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1979,7 +1979,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N3" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2026,7 +2026,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N4" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2073,7 +2073,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N5" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2120,7 +2120,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N6" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2167,7 +2167,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N7" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2214,7 +2214,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N8" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2261,7 +2261,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N9" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2308,7 +2308,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N10" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2355,7 +2355,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N11" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2402,7 +2402,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N12" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2449,7 +2449,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N13" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2496,7 +2496,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N14" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2543,7 +2543,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N15" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2590,7 +2590,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N16" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2637,7 +2637,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N17" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2684,7 +2684,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N18" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2731,7 +2731,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N19" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2778,7 +2778,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N20" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2825,7 +2825,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N21" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2872,7 +2872,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N22" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2919,7 +2919,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N23" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2966,7 +2966,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N24" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3013,7 +3013,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N25" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3060,7 +3060,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N26" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3107,7 +3107,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N27" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3154,7 +3154,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N28" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3201,7 +3201,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N29" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3248,7 +3248,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N30" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3295,7 +3295,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N31" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3342,7 +3342,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N32" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3389,7 +3389,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N33" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3436,7 +3436,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N34" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3483,7 +3483,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N35" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3530,7 +3530,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N36" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3577,7 +3577,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N37" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3624,7 +3624,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N38" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3671,7 +3671,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N39" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3718,7 +3718,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N40" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3765,7 +3765,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N41" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3812,7 +3812,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N42" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3859,7 +3859,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N43" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3906,7 +3906,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N44" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3953,7 +3953,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N45" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4000,7 +4000,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N46" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4047,7 +4047,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N47" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4094,7 +4094,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N48" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4141,7 +4141,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N49" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4188,7 +4188,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N50" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4235,7 +4235,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N51" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -4282,7 +4282,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N52" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -4329,7 +4329,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N53" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -4376,7 +4376,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N54" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -4423,7 +4423,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N55" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -4470,7 +4470,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N56" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -4517,7 +4517,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N57" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -4564,7 +4564,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N58" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -4611,7 +4611,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N59" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -4658,7 +4658,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N60" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -4705,7 +4705,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N61" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -4752,7 +4752,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N62" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -4799,7 +4799,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N63" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -4846,7 +4846,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N64" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -4893,7 +4893,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N65" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -4940,7 +4940,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N66" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -4987,7 +4987,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N67" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -5034,7 +5034,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N68" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -5081,7 +5081,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N69" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -5128,7 +5128,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N70" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -5175,7 +5175,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N71" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -5222,7 +5222,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N72" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -5269,7 +5269,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N73" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -5316,7 +5316,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N74" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -5363,7 +5363,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N75" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -5410,7 +5410,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N76" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -5457,7 +5457,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N77" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -5504,7 +5504,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N78" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -5551,7 +5551,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N79" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -5598,7 +5598,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N80" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -5645,7 +5645,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N81" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -5692,7 +5692,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N82" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -5739,7 +5739,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N83" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -5786,7 +5786,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N84" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -5833,7 +5833,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N85" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -5880,7 +5880,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N86" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -5927,7 +5927,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N87" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -5974,7 +5974,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N88" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -6021,7 +6021,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N89" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -6068,7 +6068,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N90" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -6115,7 +6115,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N91" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -6162,7 +6162,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N92" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -6209,7 +6209,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N93" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -6256,7 +6256,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N94" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -6303,7 +6303,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N95" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -6350,7 +6350,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N96" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -6397,7 +6397,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N97" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -6444,7 +6444,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N98" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -6491,7 +6491,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N99" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -6538,7 +6538,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N100" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -6585,7 +6585,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N101" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -6632,7 +6632,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N102" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -6679,7 +6679,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N103" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -6726,7 +6726,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N104" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -6773,7 +6773,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N105" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -6820,7 +6820,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N106" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -6867,7 +6867,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N107" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -6914,7 +6914,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N108" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -6961,7 +6961,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N109" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -7008,7 +7008,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N110" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -7055,7 +7055,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N111" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -7102,7 +7102,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N112" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7149,7 +7149,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N113" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -7196,7 +7196,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N114" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -7243,7 +7243,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N115" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -7290,7 +7290,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N116" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -7337,7 +7337,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N117" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -7384,7 +7384,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N118" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -7431,7 +7431,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N119" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -7478,7 +7478,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N120" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -7525,7 +7525,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N121" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -7572,7 +7572,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N122" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -7619,7 +7619,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N123" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -7666,7 +7666,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N124" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -7713,7 +7713,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N125" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -7760,7 +7760,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N126" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -7807,7 +7807,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N127" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -7854,7 +7854,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N128" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -7901,7 +7901,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N129" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -7948,7 +7948,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N130" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -7995,7 +7995,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N131" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -8042,7 +8042,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N132" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -8089,7 +8089,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N133" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -8136,7 +8136,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N134" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -8183,7 +8183,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N135" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -8230,7 +8230,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N136" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -8277,7 +8277,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N137" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -8324,7 +8324,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N138" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -8371,7 +8371,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N139" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -8418,7 +8418,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N140" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -8465,7 +8465,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N141" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -8512,7 +8512,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N142" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -8559,7 +8559,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N143" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -8606,7 +8606,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N144" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -8653,7 +8653,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N145" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -8700,7 +8700,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N146" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -8747,7 +8747,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N147" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -8794,7 +8794,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N148" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -8841,7 +8841,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N149" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -8888,7 +8888,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N150" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -8935,7 +8935,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N151" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -8982,7 +8982,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N152" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -9029,7 +9029,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N153" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -9076,7 +9076,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N154" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -9123,7 +9123,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N155" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -9170,7 +9170,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N156" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -9217,7 +9217,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N157" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -9264,7 +9264,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N158" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -9311,7 +9311,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N159" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -9358,7 +9358,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N160" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -9405,7 +9405,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N161" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -9452,7 +9452,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N162" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -9499,7 +9499,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N163" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -9546,7 +9546,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N164" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -9593,7 +9593,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N165" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -9640,7 +9640,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N166" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -9687,7 +9687,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N167" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -9734,7 +9734,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N168" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -9781,7 +9781,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N169" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -9828,7 +9828,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N170" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -9875,7 +9875,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N171" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -9922,7 +9922,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N172" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -9969,7 +9969,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N173" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -10016,7 +10016,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N174" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -10063,7 +10063,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N175" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -10110,7 +10110,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N176" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -10157,7 +10157,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N177" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -10198,7 +10198,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N178" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -10245,7 +10245,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N179" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -10292,7 +10292,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N180" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -10339,7 +10339,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N181" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -10386,7 +10386,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N182" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -10433,7 +10433,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N183" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -10480,7 +10480,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N184" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -10527,7 +10527,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N185" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -10574,7 +10574,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N186" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -10621,7 +10621,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N187" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -10668,7 +10668,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N188" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -10715,7 +10715,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N189" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -10762,7 +10762,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N190" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -10809,7 +10809,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N191" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -10856,7 +10856,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N192" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -10903,7 +10903,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N193" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -10950,7 +10950,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N194" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -10997,7 +10997,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N195" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -11044,7 +11044,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N196" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -11091,7 +11091,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N197" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -11138,7 +11138,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N198" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -11185,7 +11185,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N199" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -11232,7 +11232,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N200" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -11279,7 +11279,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N201" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -11326,7 +11326,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N202" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -11373,7 +11373,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N203" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -11420,7 +11420,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N204" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -11467,7 +11467,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N205" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -11514,7 +11514,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N206" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -11561,7 +11561,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N207" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -11608,7 +11608,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N208" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -11655,7 +11655,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N209" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -11702,7 +11702,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N210" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -11749,7 +11749,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N211" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -11796,7 +11796,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N212" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -11843,7 +11843,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N213" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -11890,7 +11890,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N214" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -11937,7 +11937,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N215" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -11984,7 +11984,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N216" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -12031,7 +12031,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N217" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -12078,7 +12078,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N218" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -12125,7 +12125,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N219" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -12172,7 +12172,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N220" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -12219,7 +12219,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N221" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -12266,7 +12266,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N222" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -12313,7 +12313,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N223" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -12360,7 +12360,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N224" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -12407,7 +12407,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N225" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -12454,7 +12454,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N226" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -12501,7 +12501,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N227" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -12548,7 +12548,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N228" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -12595,7 +12595,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N229" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -12642,7 +12642,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N230" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -12689,7 +12689,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N231" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -12736,7 +12736,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N232" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -12783,7 +12783,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N233" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -12830,7 +12830,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N234" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -12877,7 +12877,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N235" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -12924,7 +12924,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N236" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -12971,7 +12971,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N237" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -13018,7 +13018,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N238" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -13065,7 +13065,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N239" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -13112,7 +13112,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N240" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -13159,7 +13159,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N241" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -13206,7 +13206,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N242" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -13253,7 +13253,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N243" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -13300,7 +13300,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N244" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -13347,7 +13347,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N245" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -13394,7 +13394,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N246" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
@@ -13441,7 +13441,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N247" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -13488,7 +13488,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N248" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
@@ -13535,7 +13535,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N249" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -13582,7 +13582,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N250" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -13629,7 +13629,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N251" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -13676,7 +13676,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N252" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -13723,7 +13723,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N253" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -13770,7 +13770,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N254" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -13817,7 +13817,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N255" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -13864,7 +13864,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N256" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -13911,7 +13911,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N257" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -13958,7 +13958,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N258" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -14005,7 +14005,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N259" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -14052,7 +14052,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N260" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
@@ -14099,7 +14099,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N261" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -14146,7 +14146,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N262" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="263">
@@ -14193,7 +14193,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N263" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -14240,7 +14240,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N264" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
@@ -14287,7 +14287,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N265" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
@@ -14334,7 +14334,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N266" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
@@ -14381,7 +14381,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N267" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -14428,7 +14428,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N268" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
@@ -14475,7 +14475,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N269" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -14522,7 +14522,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N270" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -14569,7 +14569,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N271" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -14616,7 +14616,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N272" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
@@ -14663,7 +14663,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N273" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -14710,7 +14710,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N274" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -14757,7 +14757,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N275" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -14804,7 +14804,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N276" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
@@ -14851,7 +14851,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N277" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -14898,7 +14898,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N278" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -14945,7 +14945,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N279" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -14992,7 +14992,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N280" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -15039,7 +15039,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N281" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -15086,7 +15086,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N282" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -15133,7 +15133,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N283" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -15180,7 +15180,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N284" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -15227,7 +15227,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N285" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -15274,7 +15274,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N286" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -15321,7 +15321,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N287" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -15368,7 +15368,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N288" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -15415,7 +15415,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N289" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -15462,7 +15462,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N290" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -15509,7 +15509,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N291" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -15556,7 +15556,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N292" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -15603,7 +15603,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N293" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -15650,7 +15650,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N294" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="295">
@@ -15697,7 +15697,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N295" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -15744,7 +15744,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N296" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -15791,7 +15791,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N297" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
@@ -15838,7 +15838,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N298" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
@@ -15885,7 +15885,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N299" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
@@ -15932,7 +15932,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N300" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -15979,7 +15979,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N301" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
@@ -16026,7 +16026,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N302" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -16073,7 +16073,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N303" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -16120,7 +16120,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N304" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
@@ -16167,7 +16167,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N305" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -16214,7 +16214,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N306" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -16261,7 +16261,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N307" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
@@ -16308,7 +16308,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N308" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -16355,7 +16355,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N309" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -16402,7 +16402,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N310" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -16449,7 +16449,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N311" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
@@ -16496,7 +16496,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N312" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
@@ -16543,7 +16543,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N313" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="314">
@@ -16590,7 +16590,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N314" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -16637,7 +16637,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N315" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="316">
@@ -16684,7 +16684,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N316" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
@@ -16731,7 +16731,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N317" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
@@ -16778,7 +16778,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N318" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -16825,7 +16825,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N319" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -16872,7 +16872,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N320" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
@@ -16919,7 +16919,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N321" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
@@ -16966,7 +16966,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N322" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="323">
@@ -17013,7 +17013,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N323" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -17060,7 +17060,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N324" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -17107,7 +17107,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N325" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -17154,7 +17154,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N326" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
@@ -17201,7 +17201,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N327" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -17248,7 +17248,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N328" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
@@ -17295,7 +17295,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N329" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="330">
@@ -17342,7 +17342,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N330" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="331">
@@ -17389,7 +17389,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N331" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
@@ -17436,7 +17436,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N332" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="333">
@@ -17483,7 +17483,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N333" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="334">
@@ -17530,7 +17530,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N334" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -17577,7 +17577,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N335" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -17624,7 +17624,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N336" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
@@ -17671,7 +17671,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N337" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="338">
@@ -17718,7 +17718,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N338" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -17765,7 +17765,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N339" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
@@ -17812,7 +17812,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N340" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -17859,7 +17859,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N341" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
@@ -17906,7 +17906,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N342" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
@@ -17953,7 +17953,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N343" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -18000,7 +18000,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N344" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="345">
@@ -18047,7 +18047,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N345" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="346">
@@ -18094,7 +18094,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N346" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="347">
@@ -18141,7 +18141,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N347" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
@@ -18188,7 +18188,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N348" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -18235,7 +18235,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N349" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="350">
@@ -18282,7 +18282,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N350" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -18329,7 +18329,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N351" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -18376,7 +18376,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N352" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
@@ -18423,7 +18423,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N353" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="354">
@@ -18470,7 +18470,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N354" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -18517,7 +18517,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N355" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -18564,7 +18564,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N356" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -18611,7 +18611,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N357" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -18658,7 +18658,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N358" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="359">
@@ -18705,7 +18705,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N359" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -18752,7 +18752,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N360" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="361">
@@ -18799,7 +18799,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N361" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="362">
@@ -18846,7 +18846,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N362" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -18893,7 +18893,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N363" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -18940,7 +18940,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N364" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -18987,7 +18987,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N365" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="366">
@@ -19034,7 +19034,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N366" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="367">
@@ -19081,7 +19081,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N367" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="368">
@@ -19128,7 +19128,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N368" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="369">
@@ -19175,7 +19175,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N369" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
@@ -19222,7 +19222,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N370" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -19269,7 +19269,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N371" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -19316,7 +19316,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N372" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="373">
@@ -19363,7 +19363,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N373" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -19410,7 +19410,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N374" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -19457,7 +19457,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N375" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -19504,7 +19504,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N376" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
@@ -19551,7 +19551,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N377" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
@@ -19598,7 +19598,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N378" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -19645,7 +19645,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N379" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -19692,7 +19692,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N380" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -19739,7 +19739,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N381" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="382">
@@ -19786,7 +19786,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N382" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -19833,7 +19833,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N383" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="384">
@@ -19880,7 +19880,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N384" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -19927,7 +19927,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N385" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -19974,7 +19974,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N386" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="387">
@@ -20021,7 +20021,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N387" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -20068,7 +20068,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N388" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="389">
@@ -20115,7 +20115,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N389" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="390">
@@ -20162,7 +20162,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N390" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -20209,7 +20209,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N391" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -20256,7 +20256,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N392" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -20303,7 +20303,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N393" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
@@ -20350,7 +20350,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N394" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -20397,7 +20397,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N395" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="396">
@@ -20444,7 +20444,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N396" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="397">
@@ -20491,7 +20491,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N397" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -20538,7 +20538,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N398" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
@@ -20585,7 +20585,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N399" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
@@ -20632,7 +20632,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N400" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
@@ -20679,7 +20679,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N401" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="402">
@@ -20726,7 +20726,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N402" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="403">
@@ -20773,7 +20773,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N403" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="404">
@@ -20820,7 +20820,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N404" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="405">
@@ -20867,7 +20867,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N405" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -20914,7 +20914,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N406" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -20961,7 +20961,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N407" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
@@ -21008,7 +21008,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N408" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="409">
@@ -21055,7 +21055,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N409" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
@@ -21102,7 +21102,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N410" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="411">
@@ -21149,7 +21149,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N411" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="412">
@@ -21196,7 +21196,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N412" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="413">
@@ -21243,7 +21243,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N413" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="414">
@@ -21290,7 +21290,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N414" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="415">
@@ -21337,7 +21337,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N415" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="416">
@@ -21384,7 +21384,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N416" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="417">
@@ -21431,7 +21431,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N417" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -21478,7 +21478,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N418" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="419">
@@ -21525,7 +21525,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N419" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="420">
@@ -21572,7 +21572,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N420" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -21619,7 +21619,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N421" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -21666,7 +21666,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N422" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="423">
@@ -21713,7 +21713,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N423" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="424">
@@ -21760,7 +21760,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N424" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -21807,7 +21807,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N425" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -21854,7 +21854,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N426" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -21901,7 +21901,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N427" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -21948,7 +21948,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N428" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="429">
@@ -21995,7 +21995,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N429" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -22042,7 +22042,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N430" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -22089,7 +22089,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N431" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="432">
@@ -22136,7 +22136,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N432" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -22183,7 +22183,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N433" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -22230,7 +22230,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N434" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -22277,7 +22277,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N435" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -22324,7 +22324,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N436" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -22371,7 +22371,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N437" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="438">
@@ -22418,7 +22418,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N438" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -22465,7 +22465,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N439" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -22512,7 +22512,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N440" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="441">
@@ -22559,7 +22559,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N441" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -22606,7 +22606,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N442" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="443">
@@ -22653,7 +22653,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N443" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="444">
@@ -22700,7 +22700,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N444" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="445">
@@ -22747,7 +22747,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N445" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="446">
@@ -22794,7 +22794,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N446" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="447">
@@ -22841,7 +22841,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N447" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
@@ -22888,7 +22888,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N448" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -22935,7 +22935,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N449" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
@@ -22982,7 +22982,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N450" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -23029,7 +23029,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N451" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
@@ -23076,7 +23076,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N452" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
@@ -23123,7 +23123,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N453" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
@@ -23170,7 +23170,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N454" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
@@ -23217,7 +23217,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N455" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -23264,7 +23264,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N456" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -23311,7 +23311,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N457" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
@@ -23358,7 +23358,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N458" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
@@ -23405,7 +23405,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N459" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
@@ -23452,7 +23452,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N460" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
@@ -23499,7 +23499,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N461" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
@@ -23546,7 +23546,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N462" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -23593,7 +23593,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N463" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
@@ -23640,7 +23640,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N464" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -23687,7 +23687,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N465" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -23734,7 +23734,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N466" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -23781,7 +23781,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N467" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="468">
@@ -23828,7 +23828,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N468" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -23875,7 +23875,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N469" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -23922,7 +23922,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N470" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -23969,7 +23969,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N471" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -24016,7 +24016,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N472" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -24063,7 +24063,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N473" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="474">
@@ -24110,7 +24110,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N474" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -24157,7 +24157,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N475" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
@@ -24204,7 +24204,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N476" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -24251,7 +24251,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N477" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
@@ -24298,7 +24298,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N478" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -24345,7 +24345,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N479" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
@@ -24392,7 +24392,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N480" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -24439,7 +24439,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N481" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -24486,7 +24486,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N482" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -24533,7 +24533,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N483" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
@@ -24580,7 +24580,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N484" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -24627,7 +24627,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N485" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -24674,7 +24674,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N486" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -24721,7 +24721,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N487" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -24768,7 +24768,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N488" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
@@ -24815,7 +24815,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N489" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -24862,7 +24862,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N490" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -24909,7 +24909,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N491" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -24956,7 +24956,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N492" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -25003,7 +25003,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N493" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="494">
@@ -25050,7 +25050,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N494" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -25097,7 +25097,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N495" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
@@ -25144,7 +25144,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N496" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -25191,7 +25191,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N497" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -25238,7 +25238,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N498" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -25285,7 +25285,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N499" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -25332,7 +25332,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N500" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -25379,7 +25379,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N501" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
@@ -25426,7 +25426,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N502" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -25473,7 +25473,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N503" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
@@ -25520,7 +25520,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N504" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -25567,7 +25567,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N505" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="506">
@@ -25614,7 +25614,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N506" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -25661,7 +25661,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N507" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
@@ -25708,7 +25708,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N508" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -25755,7 +25755,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N509" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
@@ -25802,7 +25802,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N510" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -25849,7 +25849,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N511" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
@@ -25896,7 +25896,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N512" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -25943,7 +25943,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N513" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -25990,7 +25990,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N514" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -26037,7 +26037,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N515" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="516">
@@ -26084,7 +26084,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N516" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -26131,7 +26131,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N517" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
@@ -26178,7 +26178,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N518" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -26225,7 +26225,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N519" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -26272,7 +26272,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N520" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -26319,7 +26319,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N521" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="522">
@@ -26366,7 +26366,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N522" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -26413,7 +26413,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N523" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="524">
@@ -26460,7 +26460,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N524" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -26507,7 +26507,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N525" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
@@ -26554,7 +26554,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N526" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -26601,7 +26601,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N527" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
@@ -26648,7 +26648,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N528" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -26695,7 +26695,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N529" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
@@ -26742,7 +26742,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N530" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -26789,7 +26789,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N531" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -26836,7 +26836,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N532" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
@@ -26883,7 +26883,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N533" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="534">
@@ -26930,7 +26930,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N534" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -26977,7 +26977,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N535" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
@@ -27024,7 +27024,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N536" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
@@ -27071,7 +27071,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N537" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="538">
@@ -27118,7 +27118,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N538" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="539">
@@ -27165,7 +27165,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N539" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="540">
@@ -27212,7 +27212,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N540" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="541">
@@ -27259,7 +27259,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N541" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="542">
@@ -27306,7 +27306,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N542" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="543">
@@ -27353,7 +27353,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N543" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="544">
@@ -27400,7 +27400,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N544" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="545">
@@ -27447,7 +27447,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N545" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="546">
@@ -27494,7 +27494,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N546" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="547">
@@ -27541,7 +27541,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N547" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="548">
@@ -27588,7 +27588,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N548" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="549">
@@ -27635,7 +27635,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N549" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="550">
@@ -27682,7 +27682,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N550" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="551">
@@ -27729,7 +27729,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N551" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="552">
@@ -27776,7 +27776,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N552" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="553">
@@ -27823,7 +27823,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N553" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="554">
@@ -27870,7 +27870,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N554" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="555">
@@ -27917,7 +27917,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N555" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="556">
@@ -27964,7 +27964,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N556" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="557">
@@ -28011,7 +28011,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N557" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="558">
@@ -28058,7 +28058,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N558" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="559">
@@ -28105,7 +28105,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N559" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="560">
@@ -28152,7 +28152,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N560" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="561">
@@ -28191,7 +28191,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N561" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="562">
@@ -28238,7 +28238,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N562" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="563">
@@ -28285,7 +28285,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N563" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="564">
@@ -28332,7 +28332,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N564" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="565">
@@ -28379,7 +28379,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N565" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="566">
@@ -28426,7 +28426,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N566" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="567">
@@ -28473,7 +28473,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N567" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="568">
@@ -28520,7 +28520,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N568" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="569">
@@ -28567,7 +28567,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N569" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="570">
@@ -28614,7 +28614,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N570" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="571">
@@ -28661,7 +28661,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N571" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="572">
@@ -28708,7 +28708,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N572" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="573">
@@ -28755,7 +28755,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N573" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="574">
@@ -28802,7 +28802,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N574" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="575">
@@ -28849,7 +28849,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N575" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="576">
@@ -28896,7 +28896,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N576" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="577">
@@ -28943,7 +28943,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N577" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="578">
@@ -28990,7 +28990,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N578" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="579">
@@ -29037,7 +29037,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N579" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="580">
@@ -29084,7 +29084,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N580" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="581">
@@ -29131,7 +29131,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N581" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="582">
@@ -29178,7 +29178,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N582" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="583">
@@ -29225,7 +29225,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N583" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="584">
@@ -29272,7 +29272,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N584" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="585">
@@ -29319,7 +29319,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N585" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="586">
@@ -29366,7 +29366,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N586" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="587">
@@ -29413,7 +29413,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N587" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="588">
@@ -29460,7 +29460,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N588" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="589">
@@ -29507,7 +29507,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N589" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="590">
@@ -29554,7 +29554,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N590" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="591">
@@ -29601,7 +29601,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N591" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="592">
@@ -29648,7 +29648,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N592" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="593">
@@ -29695,7 +29695,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N593" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="594">
@@ -29742,7 +29742,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N594" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="595">
@@ -29789,7 +29789,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N595" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="596">
@@ -29836,7 +29836,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N596" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="597">
@@ -29883,7 +29883,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N597" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="598">
@@ -29930,7 +29930,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N598" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="599">
@@ -29950,10 +29950,10 @@
         <x:v>234.02</x:v>
       </x:c>
       <x:c r="F599" s="42" t="n">
-        <x:v>91.75</x:v>
+        <x:v>91.44</x:v>
       </x:c>
       <x:c r="G599" s="42" t="n">
-        <x:v>114.42</x:v>
+        <x:v>113.94</x:v>
       </x:c>
       <x:c r="H599" s="43" t="n">
         <x:v>2173343.6</x:v>
@@ -29967,17 +29967,17 @@
       </x:c>
       <x:c r="K599" s="42" t="n">
         <x:f>D599-F599</x:f>
-        <x:v>130.66</x:v>
+        <x:v>130.97</x:v>
       </x:c>
       <x:c r="L599" s="42" t="n">
         <x:f>E599-G599</x:f>
-        <x:v>119.60000000000001</x:v>
+        <x:v>120.08000000000001</x:v>
       </x:c>
       <x:c r="M599" s="29" t="str">
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N599" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="600">
@@ -29997,10 +29997,10 @@
         <x:v>457.62</x:v>
       </x:c>
       <x:c r="F600" s="42" t="n">
-        <x:v>147.6</x:v>
+        <x:v>146.95</x:v>
       </x:c>
       <x:c r="G600" s="42" t="n">
-        <x:v>224.59</x:v>
+        <x:v>224.51</x:v>
       </x:c>
       <x:c r="H600" s="43" t="n">
         <x:v>2319669.19</x:v>
@@ -30014,17 +30014,17 @@
       </x:c>
       <x:c r="K600" s="42" t="n">
         <x:f>D600-F600</x:f>
-        <x:v>197.29999999999998</x:v>
+        <x:v>197.95</x:v>
       </x:c>
       <x:c r="L600" s="42" t="n">
         <x:f>E600-G600</x:f>
-        <x:v>233.03</x:v>
+        <x:v>233.11</x:v>
       </x:c>
       <x:c r="M600" s="29" t="str">
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N600" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="601">
@@ -30044,10 +30044,10 @@
         <x:v>507.14</x:v>
       </x:c>
       <x:c r="F601" s="42" t="n">
-        <x:v>308.82</x:v>
+        <x:v>309.07</x:v>
       </x:c>
       <x:c r="G601" s="42" t="n">
-        <x:v>364.2</x:v>
+        <x:v>364.48</x:v>
       </x:c>
       <x:c r="H601" s="43" t="n">
         <x:v>2478095.76</x:v>
@@ -30061,17 +30061,17 @@
       </x:c>
       <x:c r="K601" s="42" t="n">
         <x:f>D601-F601</x:f>
-        <x:v>120.26999999999998</x:v>
+        <x:v>120.01999999999998</x:v>
       </x:c>
       <x:c r="L601" s="42" t="n">
         <x:f>E601-G601</x:f>
-        <x:v>142.94</x:v>
+        <x:v>142.65999999999997</x:v>
       </x:c>
       <x:c r="M601" s="29" t="str">
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N601" s="41" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
     <x:row r="602">
@@ -30091,10 +30091,10 @@
         <x:v>419.54</x:v>
       </x:c>
       <x:c r="F602" s="42" t="n">
-        <x:v>179.52</x:v>
+        <x:v>178.91</x:v>
       </x:c>
       <x:c r="G602" s="42" t="n">
-        <x:v>251.28</x:v>
+        <x:v>250.52</x:v>
       </x:c>
       <x:c r="H602" s="43" t="n">
         <x:v>2457198.12</x:v>
@@ -30108,17 +30108,252 @@
       </x:c>
       <x:c r="K602" s="42" t="n">
         <x:f>D602-F602</x:f>
-        <x:v>152.39000000000001</x:v>
+        <x:v>153.00000000000003</x:v>
       </x:c>
       <x:c r="L602" s="42" t="n">
         <x:f>E602-G602</x:f>
-        <x:v>168.26000000000002</x:v>
+        <x:v>169.02</x:v>
       </x:c>
       <x:c r="M602" s="29" t="str">
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N602" s="41" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603">
+      <x:c r="A603" s="41" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="B603" s="42" t="n">
+        <x:v>299.71</x:v>
+      </x:c>
+      <x:c r="C603" s="42" t="n">
+        <x:v>283.58</x:v>
+      </x:c>
+      <x:c r="D603" s="42" t="n">
+        <x:v>326.41</x:v>
+      </x:c>
+      <x:c r="E603" s="42" t="n">
+        <x:v>315.33</x:v>
+      </x:c>
+      <x:c r="F603" s="42" t="n">
+        <x:v>218.2</x:v>
+      </x:c>
+      <x:c r="G603" s="42" t="n">
+        <x:v>193.17</x:v>
+      </x:c>
+      <x:c r="H603" s="43" t="n">
+        <x:v>2610328.82</x:v>
+      </x:c>
+      <x:c r="I603" s="43" t="n">
+        <x:v>2544299.85</x:v>
+      </x:c>
+      <x:c r="J603" s="42" t="n">
+        <x:f>B603-C603</x:f>
+        <x:v>16.129999999999995</x:v>
+      </x:c>
+      <x:c r="K603" s="42" t="n">
+        <x:f>D603-F603</x:f>
+        <x:v>108.21000000000004</x:v>
+      </x:c>
+      <x:c r="L603" s="42" t="n">
+        <x:f>E603-G603</x:f>
+        <x:v>122.16</x:v>
+      </x:c>
+      <x:c r="M603" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N603" s="41" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604">
+      <x:c r="A604" s="41" t="n">
         <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B604" s="42" t="n">
+        <x:v>408.85</x:v>
+      </x:c>
+      <x:c r="C604" s="42" t="n">
+        <x:v>535.34</x:v>
+      </x:c>
+      <x:c r="D604" s="42" t="n">
+        <x:v>424.35</x:v>
+      </x:c>
+      <x:c r="E604" s="42" t="n">
+        <x:v>551.74</x:v>
+      </x:c>
+      <x:c r="F604" s="42" t="n">
+        <x:v>336.06</x:v>
+      </x:c>
+      <x:c r="G604" s="42" t="n">
+        <x:v>419.29</x:v>
+      </x:c>
+      <x:c r="H604" s="43" t="n">
+        <x:v>2714597.4</x:v>
+      </x:c>
+      <x:c r="I604" s="43" t="n">
+        <x:v>2774558.94</x:v>
+      </x:c>
+      <x:c r="J604" s="42" t="n">
+        <x:f>B604-C604</x:f>
+        <x:v>-126.49000000000001</x:v>
+      </x:c>
+      <x:c r="K604" s="42" t="n">
+        <x:f>D604-F604</x:f>
+        <x:v>88.29000000000002</x:v>
+      </x:c>
+      <x:c r="L604" s="42" t="n">
+        <x:f>E604-G604</x:f>
+        <x:v>132.45</x:v>
+      </x:c>
+      <x:c r="M604" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N604" s="41" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605">
+      <x:c r="A605" s="41" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="B605" s="42" t="n">
+        <x:v>414.23</x:v>
+      </x:c>
+      <x:c r="C605" s="42" t="n">
+        <x:v>437.34</x:v>
+      </x:c>
+      <x:c r="D605" s="42" t="n">
+        <x:v>415.2</x:v>
+      </x:c>
+      <x:c r="E605" s="42" t="n">
+        <x:v>435.87</x:v>
+      </x:c>
+      <x:c r="F605" s="42" t="n">
+        <x:v>406.39</x:v>
+      </x:c>
+      <x:c r="G605" s="42" t="n">
+        <x:v>438.38</x:v>
+      </x:c>
+      <x:c r="H605" s="43" t="n">
+        <x:v>2880473.18</x:v>
+      </x:c>
+      <x:c r="I605" s="43" t="n">
+        <x:v>2886656.45</x:v>
+      </x:c>
+      <x:c r="J605" s="42" t="n">
+        <x:f>B605-C605</x:f>
+        <x:v>-23.109999999999957</x:v>
+      </x:c>
+      <x:c r="K605" s="42" t="n">
+        <x:f>D605-F605</x:f>
+        <x:v>8.810000000000002</x:v>
+      </x:c>
+      <x:c r="L605" s="42" t="n">
+        <x:f>E605-G605</x:f>
+        <x:v>-2.509999999999991</x:v>
+      </x:c>
+      <x:c r="M605" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N605" s="41" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606">
+      <x:c r="A606" s="41" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="B606" s="42" t="n">
+        <x:v>472.75</x:v>
+      </x:c>
+      <x:c r="C606" s="42" t="n">
+        <x:v>331.83</x:v>
+      </x:c>
+      <x:c r="D606" s="42" t="n">
+        <x:v>462.1</x:v>
+      </x:c>
+      <x:c r="E606" s="42" t="n">
+        <x:v>329.57</x:v>
+      </x:c>
+      <x:c r="F606" s="42" t="n">
+        <x:v>527.34</x:v>
+      </x:c>
+      <x:c r="G606" s="42" t="n">
+        <x:v>330.76</x:v>
+      </x:c>
+      <x:c r="H606" s="43" t="n">
+        <x:v>2796021.05</x:v>
+      </x:c>
+      <x:c r="I606" s="43" t="n">
+        <x:v>2496559.75</x:v>
+      </x:c>
+      <x:c r="J606" s="42" t="n">
+        <x:f>B606-C606</x:f>
+        <x:v>140.92000000000002</x:v>
+      </x:c>
+      <x:c r="K606" s="42" t="n">
+        <x:f>D606-F606</x:f>
+        <x:v>-65.24000000000001</x:v>
+      </x:c>
+      <x:c r="L606" s="42" t="n">
+        <x:f>E606-G606</x:f>
+        <x:v>-1.1899999999999977</x:v>
+      </x:c>
+      <x:c r="M606" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N606" s="41" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607">
+      <x:c r="A607" s="41" t="n">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="B607" s="42" t="n">
+        <x:v>172.48</x:v>
+      </x:c>
+      <x:c r="C607" s="42" t="n">
+        <x:v>188.04</x:v>
+      </x:c>
+      <x:c r="D607" s="42" t="n">
+        <x:v>199.49</x:v>
+      </x:c>
+      <x:c r="E607" s="42" t="n">
+        <x:v>207.32</x:v>
+      </x:c>
+      <x:c r="F607" s="42" t="n">
+        <x:v>80.24</x:v>
+      </x:c>
+      <x:c r="G607" s="42" t="n">
+        <x:v>114.2</x:v>
+      </x:c>
+      <x:c r="H607" s="43" t="n">
+        <x:v>2138169.04</x:v>
+      </x:c>
+      <x:c r="I607" s="43" t="n">
+        <x:v>2160900.95</x:v>
+      </x:c>
+      <x:c r="J607" s="42" t="n">
+        <x:f>B607-C607</x:f>
+        <x:v>-15.560000000000002</x:v>
+      </x:c>
+      <x:c r="K607" s="42" t="n">
+        <x:f>D607-F607</x:f>
+        <x:v>119.25000000000001</x:v>
+      </x:c>
+      <x:c r="L607" s="42" t="n">
+        <x:f>E607-G607</x:f>
+        <x:v>93.11999999999999</x:v>
+      </x:c>
+      <x:c r="M607" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N607" s="41" t="n">
+        <x:v>46265</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -63171,13 +63406,287 @@
       <x:c r="P602" s="42"/>
       <x:c r="Q602" s="42"/>
       <x:c r="R602" s="29" t="str">
-        <x:v>公众号未发布</x:v>
+        <x:v>公众号日报缺失</x:v>
       </x:c>
       <x:c r="S602" s="45"/>
       <x:c r="T602" s="29"/>
     </x:row>
+    <x:row r="603">
+      <x:c r="A603" s="41" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="B603" s="42"/>
+      <x:c r="C603" s="42"/>
+      <x:c r="D603" s="42"/>
+      <x:c r="E603" s="42"/>
+      <x:c r="F603" s="42"/>
+      <x:c r="G603" s="42"/>
+      <x:c r="H603" s="42"/>
+      <x:c r="I603" s="42"/>
+      <x:c r="J603" s="42"/>
+      <x:c r="K603" s="42"/>
+      <x:c r="L603" s="42"/>
+      <x:c r="M603" s="42"/>
+      <x:c r="N603" s="42"/>
+      <x:c r="O603" s="42"/>
+      <x:c r="P603" s="42"/>
+      <x:c r="Q603" s="42"/>
+      <x:c r="R603" s="29" t="str">
+        <x:v>公众号日报缺失</x:v>
+      </x:c>
+      <x:c r="S603" s="45"/>
+      <x:c r="T603" s="29"/>
+    </x:row>
+    <x:row r="604">
+      <x:c r="A604" s="41" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B604" s="42" t="n">
+        <x:v>369.22</x:v>
+      </x:c>
+      <x:c r="C604" s="42" t="n">
+        <x:v>307.15</x:v>
+      </x:c>
+      <x:c r="D604" s="42" t="n">
+        <x:v>440.01</x:v>
+      </x:c>
+      <x:c r="E604" s="42" t="n">
+        <x:v>402.48</x:v>
+      </x:c>
+      <x:c r="F604" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G604" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H604" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I604" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J604" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="K604" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L604" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M604" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N604" s="42" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="O604" s="42" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="P604" s="42" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="Q604" s="42" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="R604" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S604" s="45" t="n">
+        <x:v>0.9382590651512146</x:v>
+      </x:c>
+      <x:c r="T604" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508338&amp;idx=1&amp;sn=2063c8ffa3238439af73f400b2a0e7aa&amp;chksm=f9f995c8ce8e1cde31e524fb31a3d39f054f4256058cb530af0731ec27ca6338b24dd7df6ce3#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605">
+      <x:c r="A605" s="41" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="B605" s="42" t="n">
+        <x:v>428.38</x:v>
+      </x:c>
+      <x:c r="C605" s="42" t="n">
+        <x:v>389.03</x:v>
+      </x:c>
+      <x:c r="D605" s="42" t="n">
+        <x:v>461.75</x:v>
+      </x:c>
+      <x:c r="E605" s="42" t="n">
+        <x:v>418.91</x:v>
+      </x:c>
+      <x:c r="F605" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G605" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H605" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I605" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J605" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="K605" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L605" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M605" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N605" s="42" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="O605" s="42" t="n">
+        <x:v>0.61</x:v>
+      </x:c>
+      <x:c r="P605" s="42" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="Q605" s="42" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="R605" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S605" s="45" t="n">
+        <x:v>0.9998060464859009</x:v>
+      </x:c>
+      <x:c r="T605" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508352&amp;idx=1&amp;sn=82979932a256acbfa4ad8e78d33fa8a4&amp;chksm=f9f9953ace8e1c2c595c0c758924a4ba7eb84feed8030e878f7c33d16f72090e0395b1ddd88c#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606">
+      <x:c r="A606" s="41" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="B606" s="42" t="n">
+        <x:v>469.13</x:v>
+      </x:c>
+      <x:c r="C606" s="42" t="n">
+        <x:v>586.86</x:v>
+      </x:c>
+      <x:c r="D606" s="42" t="n">
+        <x:v>310.88</x:v>
+      </x:c>
+      <x:c r="E606" s="42" t="n">
+        <x:v>349.38</x:v>
+      </x:c>
+      <x:c r="F606" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G606" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H606" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I606" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J606" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="K606" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L606" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M606" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N606" s="42" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="O606" s="42" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="P606" s="42" t="n">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="Q606" s="42" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="R606" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S606" s="45" t="n">
+        <x:v>0.9999802112579346</x:v>
+      </x:c>
+      <x:c r="T606" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508371&amp;idx=1&amp;sn=49af8097abeedc3d4050d435d277067d&amp;chksm=f9f99529ce8e1c3f7723ad6da560aca343f3008752060a04c5c1803255f840e20f478316411e#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607">
+      <x:c r="A607" s="41" t="n">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="B607" s="42" t="n">
+        <x:v>131.43</x:v>
+      </x:c>
+      <x:c r="C607" s="42" t="n">
+        <x:v>51.06</x:v>
+      </x:c>
+      <x:c r="D607" s="42" t="n">
+        <x:v>120.06</x:v>
+      </x:c>
+      <x:c r="E607" s="42" t="n">
+        <x:v>109.84</x:v>
+      </x:c>
+      <x:c r="F607" s="42" t="n">
+        <x:v>520.84</x:v>
+      </x:c>
+      <x:c r="G607" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H607" s="42" t="n">
+        <x:v>520.84</x:v>
+      </x:c>
+      <x:c r="I607" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J607" s="42" t="n">
+        <x:v>490.98</x:v>
+      </x:c>
+      <x:c r="K607" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L607" s="42" t="n">
+        <x:v>490.98</x:v>
+      </x:c>
+      <x:c r="M607" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N607" s="42" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="O607" s="42" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="P607" s="42" t="n">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="Q607" s="42" t="n">
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="R607" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S607" s="45" t="n">
+        <x:v>0.9999940991401672</x:v>
+      </x:c>
+      <x:c r="T607" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508373&amp;idx=1&amp;sn=5775242f01351f95255fc9f692487e0a&amp;chksm=f9f9952fce8e1c39a0297087156ea17c215674d58075aa2b2cc1929653b3809fae91c95c45e3#rd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="R2:R602">
+  <x:conditionalFormatting sqref="R2:R607">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>R2="ok"</x:formula>
     </x:cfRule>
@@ -63289,27 +63798,27 @@
         <x:v>45658</x:v>
       </x:c>
       <x:c r="B5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>329.55612903225807</x:v>
       </x:c>
       <x:c r="C5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>363.4670967741936</x:v>
       </x:c>
       <x:c r="D5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>351.32580645161295</x:v>
       </x:c>
       <x:c r="E5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>385.76935483870983</x:v>
       </x:c>
       <x:c r="F5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>215.62870967741932</x:v>
       </x:c>
       <x:c r="G5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A5,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>246.1216129032258</x:v>
       </x:c>
       <x:c r="H5" s="39" t="n">
@@ -63322,27 +63831,27 @@
         <x:v>45689</x:v>
       </x:c>
       <x:c r="B6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>300.44928571428574</x:v>
       </x:c>
       <x:c r="C6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>260.71535714285716</x:v>
       </x:c>
       <x:c r="D6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>328.29571428571427</x:v>
       </x:c>
       <x:c r="E6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>279.91249999999997</x:v>
       </x:c>
       <x:c r="F6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>178.16428571428574</x:v>
       </x:c>
       <x:c r="G6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A6,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>177.3103571428571</x:v>
       </x:c>
       <x:c r="H6" s="39" t="n">
@@ -63355,27 +63864,27 @@
         <x:v>45717</x:v>
       </x:c>
       <x:c r="B7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>279.8206451612903</x:v>
       </x:c>
       <x:c r="C7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>249.16709677419354</x:v>
       </x:c>
       <x:c r="D7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>312.7683870967742</x:v>
       </x:c>
       <x:c r="E7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>276.3945161290322</x:v>
       </x:c>
       <x:c r="F7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>171.45032258064512</x:v>
       </x:c>
       <x:c r="G7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A7,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>160.2796774193548</x:v>
       </x:c>
       <x:c r="H7" s="39" t="n">
@@ -63388,27 +63897,27 @@
         <x:v>45748</x:v>
       </x:c>
       <x:c r="B8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>220.40933333333334</x:v>
       </x:c>
       <x:c r="C8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>227.9486666666667</x:v>
       </x:c>
       <x:c r="D8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>262.6410000000001</x:v>
       </x:c>
       <x:c r="E8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>269.39033333333333</x:v>
       </x:c>
       <x:c r="F8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>123.596</x:v>
       </x:c>
       <x:c r="G8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A8,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>131.11266666666668</x:v>
       </x:c>
       <x:c r="H8" s="39" t="n">
@@ -63421,27 +63930,27 @@
         <x:v>45778</x:v>
       </x:c>
       <x:c r="B9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>216.26193548387099</x:v>
       </x:c>
       <x:c r="C9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>213.6558064516129</x:v>
       </x:c>
       <x:c r="D9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>249.0003225806452</x:v>
       </x:c>
       <x:c r="E9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>244.5761290322581</x:v>
       </x:c>
       <x:c r="F9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>131.72161290322578</x:v>
       </x:c>
       <x:c r="G9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A9,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>132.73967741935485</x:v>
       </x:c>
       <x:c r="H9" s="39" t="n">
@@ -63454,27 +63963,27 @@
         <x:v>45809</x:v>
       </x:c>
       <x:c r="B10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>237.06566666666671</x:v>
       </x:c>
       <x:c r="C10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>242.62517241379314</x:v>
       </x:c>
       <x:c r="D10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>267.17533333333336</x:v>
       </x:c>
       <x:c r="E10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>266.20965517241376</x:v>
       </x:c>
       <x:c r="F10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>134.40133333333333</x:v>
       </x:c>
       <x:c r="G10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A10,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>155.09344827586207</x:v>
       </x:c>
       <x:c r="H10" s="39" t="n">
@@ -63487,27 +63996,27 @@
         <x:v>45839</x:v>
       </x:c>
       <x:c r="B11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>251.60870967741943</x:v>
       </x:c>
       <x:c r="C11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>255.76096774193545</x:v>
       </x:c>
       <x:c r="D11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>281.05580645161297</x:v>
       </x:c>
       <x:c r="E11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>279.63709677419354</x:v>
       </x:c>
       <x:c r="F11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>136.8290322580645</x:v>
       </x:c>
       <x:c r="G11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A11,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>157.16032258064516</x:v>
       </x:c>
       <x:c r="H11" s="39" t="n">
@@ -63520,27 +64029,27 @@
         <x:v>45870</x:v>
       </x:c>
       <x:c r="B12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>298.37354838709683</x:v>
       </x:c>
       <x:c r="C12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>295.5012903225807</x:v>
       </x:c>
       <x:c r="D12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>332.4093548387097</x:v>
       </x:c>
       <x:c r="E12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>323.1909677419355</x:v>
       </x:c>
       <x:c r="F12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>151.3493548387097</x:v>
       </x:c>
       <x:c r="G12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A12,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>169.80516129032256</x:v>
       </x:c>
       <x:c r="H12" s="39" t="n">
@@ -63553,27 +64062,27 @@
         <x:v>45901</x:v>
       </x:c>
       <x:c r="B13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>144.22233333333335</x:v>
       </x:c>
       <x:c r="C13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>200.23433333333338</x:v>
       </x:c>
       <x:c r="D13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>164.3046666666666</x:v>
       </x:c>
       <x:c r="E13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>218.50633333333334</x:v>
       </x:c>
       <x:c r="F13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>95.92533333333337</x:v>
       </x:c>
       <x:c r="G13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A13,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>152.36366666666666</x:v>
       </x:c>
       <x:c r="H13" s="39" t="n">
@@ -63586,27 +64095,27 @@
         <x:v>45931</x:v>
       </x:c>
       <x:c r="B14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>257.27516129032256</x:v>
       </x:c>
       <x:c r="C14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>319.4687096774194</x:v>
       </x:c>
       <x:c r="D14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>279.0945161290323</x:v>
       </x:c>
       <x:c r="E14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>340.140322580645</x:v>
       </x:c>
       <x:c r="F14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>171.19580645161287</x:v>
       </x:c>
       <x:c r="G14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A14,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>228.87322580645167</x:v>
       </x:c>
       <x:c r="H14" s="39" t="n">
@@ -63619,27 +64128,27 @@
         <x:v>45962</x:v>
       </x:c>
       <x:c r="B15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>187.08299999999994</x:v>
       </x:c>
       <x:c r="C15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>208.76566666666668</x:v>
       </x:c>
       <x:c r="D15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>208.34633333333332</x:v>
       </x:c>
       <x:c r="E15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>231.30599999999998</x:v>
       </x:c>
       <x:c r="F15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>103.11566666666664</x:v>
       </x:c>
       <x:c r="G15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A15,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>115.58999999999999</x:v>
       </x:c>
       <x:c r="H15" s="39" t="n">
@@ -63652,27 +64161,27 @@
         <x:v>45992</x:v>
       </x:c>
       <x:c r="B16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>271.9325806451613</x:v>
       </x:c>
       <x:c r="C16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>273.27806451612906</x:v>
       </x:c>
       <x:c r="D16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>299.0351612903226</x:v>
       </x:c>
       <x:c r="E16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>299.65322580645164</x:v>
       </x:c>
       <x:c r="F16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>140.0470967741936</x:v>
       </x:c>
       <x:c r="G16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A16,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>139.21290322580646</x:v>
       </x:c>
       <x:c r="H16" s="39" t="n">
@@ -63685,27 +64194,27 @@
         <x:v>46023</x:v>
       </x:c>
       <x:c r="B17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>279.0032258064516</x:v>
       </x:c>
       <x:c r="C17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>271.9425806451613</x:v>
       </x:c>
       <x:c r="D17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>300.0367741935484</x:v>
       </x:c>
       <x:c r="E17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>289.38000000000005</x:v>
       </x:c>
       <x:c r="F17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>180.67709677419356</x:v>
       </x:c>
       <x:c r="G17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A17,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>186.3467741935484</x:v>
       </x:c>
       <x:c r="H17" s="39" t="n">
@@ -63718,27 +64227,27 @@
         <x:v>46054</x:v>
       </x:c>
       <x:c r="B18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>208.5582142857143</x:v>
       </x:c>
       <x:c r="C18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>199.73857142857145</x:v>
       </x:c>
       <x:c r="D18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>238.7057142857143</x:v>
       </x:c>
       <x:c r="E18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>225.0778571428571</x:v>
       </x:c>
       <x:c r="F18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>98.31035714285713</x:v>
       </x:c>
       <x:c r="G18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A18,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>103.44857142857143</x:v>
       </x:c>
       <x:c r="H18" s="39" t="n">
@@ -63751,27 +64260,27 @@
         <x:v>46082</x:v>
       </x:c>
       <x:c r="B19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>214.751935483871</x:v>
       </x:c>
       <x:c r="C19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>210.5164516129032</x:v>
       </x:c>
       <x:c r="D19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>245.5132258064516</x:v>
       </x:c>
       <x:c r="E19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>237.59838709677413</x:v>
       </x:c>
       <x:c r="F19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>123.60064516129032</x:v>
       </x:c>
       <x:c r="G19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A19,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>129.11387096774195</x:v>
       </x:c>
       <x:c r="H19" s="39" t="n">
@@ -63784,27 +64293,27 @@
         <x:v>46113</x:v>
       </x:c>
       <x:c r="B20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>159.10166666666666</x:v>
       </x:c>
       <x:c r="C20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>159.5346666666667</x:v>
       </x:c>
       <x:c r="D20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>204.07900000000004</x:v>
       </x:c>
       <x:c r="E20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>199.92633333333336</x:v>
       </x:c>
       <x:c r="F20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>77.90900000000002</x:v>
       </x:c>
       <x:c r="G20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A20,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>85.97333333333333</x:v>
       </x:c>
       <x:c r="H20" s="39" t="n">
@@ -63817,27 +64326,27 @@
         <x:v>46143</x:v>
       </x:c>
       <x:c r="B21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>143.0783870967742</x:v>
       </x:c>
       <x:c r="C21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>149.3541935483871</x:v>
       </x:c>
       <x:c r="D21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>175.76451612903227</x:v>
       </x:c>
       <x:c r="E21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>185.0235483870968</x:v>
       </x:c>
       <x:c r="F21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>72.17032258064515</x:v>
       </x:c>
       <x:c r="G21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A21,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>72.60258064516127</x:v>
       </x:c>
       <x:c r="H21" s="39" t="n">
@@ -63850,27 +64359,27 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>178.90266666666665</x:v>
       </x:c>
       <x:c r="C22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>174.07900000000006</x:v>
       </x:c>
       <x:c r="D22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>216.8056666666667</x:v>
       </x:c>
       <x:c r="E22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>211.91700000000003</x:v>
       </x:c>
       <x:c r="F22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>99.698</x:v>
       </x:c>
       <x:c r="G22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A22,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>96.31866666666669</x:v>
       </x:c>
       <x:c r="H22" s="39" t="n">
@@ -63883,27 +64392,27 @@
         <x:v>46204</x:v>
       </x:c>
       <x:c r="B23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
         <x:v>291.8641935483871</x:v>
       </x:c>
       <x:c r="C23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
         <x:v>293.24677419354845</x:v>
       </x:c>
       <x:c r="D23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
         <x:v>317.33600000000007</x:v>
       </x:c>
       <x:c r="E23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
         <x:v>317.49</x:v>
       </x:c>
       <x:c r="F23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
         <x:v>199.67500000000004</x:v>
       </x:c>
       <x:c r="G23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A23,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
         <x:v>204.3896666666666</x:v>
       </x:c>
       <x:c r="H23" s="39" t="n">
@@ -63916,32 +64425,32 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1),'每日数据'!$B$2:$B$602,"&lt;&gt;"),"")</x:f>
-        <x:v>202.52125</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:v>228.57000000000002</x:v>
       </x:c>
       <x:c r="C24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1),'每日数据'!$C$2:$C$602,"&lt;&gt;"),"")</x:f>
-        <x:v>215.30458333333328</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:v>239.42896551724132</x:v>
       </x:c>
       <x:c r="D24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1),'每日数据'!$D$2:$D$602,"&lt;&gt;"),"")</x:f>
-        <x:v>228.74249999999998</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:v>252.32310344827584</x:v>
       </x:c>
       <x:c r="E24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1),'每日数据'!$E$2:$E$602,"&lt;&gt;"),"")</x:f>
-        <x:v>242.75583333333336</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:v>264.34379310344826</x:v>
       </x:c>
       <x:c r="F24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1),'每日数据'!$F$2:$F$602,"&lt;&gt;"),"")</x:f>
-        <x:v>112.15791666666668</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:v>146.85172413793103</x:v>
       </x:c>
       <x:c r="G24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$602,'每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$602,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$602,"&lt;"&amp;EDATE($A24,1),'每日数据'!$G$2:$G$602,"&lt;&gt;"),"")</x:f>
-        <x:v>123.60791666666665</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:v>153.83965517241379</x:v>
       </x:c>
       <x:c r="H24" s="39" t="n">
         <x:f>B24-C24</x:f>
-        <x:v>-12.783333333333275</x:v>
+        <x:v>-10.858965517241302</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -64544,27 +65053,27 @@
       </x:c>
       <x:c r="B60" t="n">
         <x:f>B24</x:f>
-        <x:v>202.52125</x:v>
+        <x:v>228.57000000000002</x:v>
       </x:c>
       <x:c r="C60" t="n">
         <x:f>C24</x:f>
-        <x:v>215.30458333333328</x:v>
+        <x:v>239.42896551724132</x:v>
       </x:c>
       <x:c r="D60" t="n">
         <x:f>D24</x:f>
-        <x:v>228.74249999999998</x:v>
+        <x:v>252.32310344827584</x:v>
       </x:c>
       <x:c r="E60" t="n">
         <x:f>E24</x:f>
-        <x:v>242.75583333333336</x:v>
+        <x:v>264.34379310344826</x:v>
       </x:c>
       <x:c r="F60" t="n">
         <x:f>F24</x:f>
-        <x:v>112.15791666666668</x:v>
+        <x:v>146.85172413793103</x:v>
       </x:c>
       <x:c r="G60" t="n">
         <x:f>G24</x:f>
-        <x:v>123.60791666666665</x:v>
+        <x:v>153.83965517241379</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -64573,7 +65082,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00ed484c810f4973"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9baa7fcae0e4d86"/>
 </x:worksheet>
 </file>
 
@@ -65131,24 +65640,24 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$B$579:$B$602)</x:f>
-        <x:v>215.24478260869566</x:v>
+        <x:f>AVERAGE('风光分项'!$B$579:$B$607)</x:f>
+        <x:v>235.1403703703704</x:v>
       </x:c>
       <x:c r="C24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$C$579:$C$602)</x:f>
-        <x:v>67.24347826086957</x:v>
+        <x:f>AVERAGE('风光分项'!$C$579:$C$607)</x:f>
+        <x:v>106.69259259259259</x:v>
       </x:c>
       <x:c r="D24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$D$579:$D$602)</x:f>
-        <x:v>208.75434782608693</x:v>
+        <x:f>AVERAGE('风光分项'!$D$579:$D$607)</x:f>
+        <x:v>227.18703703703704</x:v>
       </x:c>
       <x:c r="E24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$E$579:$E$602)</x:f>
-        <x:v>74.42173913043477</x:v>
+        <x:f>AVERAGE('风光分项'!$E$579:$E$607)</x:f>
+        <x:v>110.82629629629629</x:v>
       </x:c>
       <x:c r="F24" s="53" t="n">
-        <x:f>COUNT('风光分项'!$B$579:$B$602)</x:f>
-        <x:v>23</x:v>
+        <x:f>COUNT('风光分项'!$B$579:$B$607)</x:f>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -65527,19 +66036,19 @@
       </x:c>
       <x:c r="B57" t="n">
         <x:f>B24</x:f>
-        <x:v>215.24478260869566</x:v>
+        <x:v>235.1403703703704</x:v>
       </x:c>
       <x:c r="C57" t="n">
         <x:f>C24</x:f>
-        <x:v>67.24347826086957</x:v>
+        <x:v>106.69259259259259</x:v>
       </x:c>
       <x:c r="D57" t="n">
         <x:f>D24</x:f>
-        <x:v>208.75434782608693</x:v>
+        <x:v>227.18703703703704</x:v>
       </x:c>
       <x:c r="E57" t="n">
         <x:f>E24</x:f>
-        <x:v>74.42173913043477</x:v>
+        <x:v>110.82629629629629</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -65548,7 +66057,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14fc8dfa51cb4160"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61d1092449c43ef"/>
 </x:worksheet>
 </file>
 
@@ -65590,28 +66099,28 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-24；同一自然日一行，共 601 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -65642,11 +66151,11 @@
         <x:v>日期行数</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:f>COUNTA('每日数据'!$A$2:$A$602)</x:f>
-        <x:v>601</x:v>
+        <x:f>COUNTA('每日数据'!$A$2:$A$607)</x:f>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="C5" s="14" t="n">
-        <x:v>601</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="D5" s="14" t="n">
         <x:f>B5-C5</x:f>
@@ -65668,7 +66177,7 @@
         <x:v>最早日期</x:v>
       </x:c>
       <x:c r="B6" s="15" t="n">
-        <x:f>MIN('每日数据'!$A$2:$A$602)</x:f>
+        <x:f>MIN('每日数据'!$A$2:$A$607)</x:f>
         <x:v>45658</x:v>
       </x:c>
       <x:c r="C6" s="15" t="n">
@@ -65694,11 +66203,11 @@
         <x:v>最晚日期</x:v>
       </x:c>
       <x:c r="B7" s="15" t="n">
-        <x:f>MAX('每日数据'!$A$2:$A$602)</x:f>
-        <x:v>46258</x:v>
+        <x:f>MAX('每日数据'!$A$2:$A$607)</x:f>
+        <x:v>46263</x:v>
       </x:c>
       <x:c r="C7" s="15" t="n">
-        <x:v>46258</x:v>
+        <x:v>46263</x:v>
       </x:c>
       <x:c r="D7" s="57" t="n">
         <x:f>B7-C7</x:f>
@@ -65720,11 +66229,11 @@
         <x:v>六类价格完整数</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:f>COUNT('每日数据'!$B$2:$G$602)</x:f>
-        <x:v>3599</x:v>
+        <x:f>COUNT('每日数据'!$B$2:$G$607)</x:f>
+        <x:v>3629</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>3599</x:v>
+        <x:v>3629</x:v>
       </x:c>
       <x:c r="D8" s="14" t="n">
         <x:f>B8-C8</x:f>
@@ -65738,7 +66247,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>理论3606；源站已知空值7个，保留为空</x:v>
+        <x:v>理论3636；源站已知空值7个，保留为空</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -65746,11 +66255,11 @@
         <x:v>总体电量完整数</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:f>COUNT('每日数据'!$H$2:$I$602)</x:f>
-        <x:v>1202</x:v>
+        <x:f>COUNT('每日数据'!$H$2:$I$607)</x:f>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
-        <x:v>1202</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="D9" s="14" t="n">
         <x:f>B9-C9</x:f>
@@ -65764,7 +66273,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>理论1202；源站已知空值0个，保留为空</x:v>
+        <x:v>理论1212；源站已知空值0个，保留为空</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
@@ -65772,7 +66281,7 @@
         <x:v>重复日期数</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
-        <x:f>SUMPRODUCT(--(COUNTIF('每日数据'!$A$2:$A$602,'每日数据'!$A$2:$A$602)&gt;1))</x:f>
+        <x:f>SUMPRODUCT(--(COUNTIF('每日数据'!$A$2:$A$607,'每日数据'!$A$2:$A$607)&gt;1))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="14" t="n">
@@ -65798,11 +66307,11 @@
         <x:v>风光四类均价完整数</x:v>
       </x:c>
       <x:c r="B11" s="14" t="n">
-        <x:f>COUNT('风光分项'!$B$2:$E$602)</x:f>
-        <x:v>2016</x:v>
+        <x:f>COUNT('风光分项'!$B$2:$E$607)</x:f>
+        <x:v>2032</x:v>
       </x:c>
       <x:c r="C11" s="14" t="n">
-        <x:v>2016</x:v>
+        <x:v>2032</x:v>
       </x:c>
       <x:c r="D11" s="14" t="n">
         <x:f>B11-C11</x:f>
@@ -65816,7 +66325,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>504个披露日×4列</x:v>
+        <x:v>508个披露日×4列</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
@@ -65824,7 +66333,7 @@
         <x:v>风光OCR待复核数</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:f>COUNTIF('风光分项'!$R$2:$R$602,"ocr_review")+COUNTIF('风光分项'!$R$2:$R$602,"range_review")+COUNTIF('风光分项'!$R$2:$R$602,"confidence_review")+COUNTIF('风光分项'!$R$2:$R$602,"待复核")</x:f>
+        <x:f>COUNTIF('风光分项'!$R$2:$R$607,"ocr_review")+COUNTIF('风光分项'!$R$2:$R$607,"range_review")+COUNTIF('风光分项'!$R$2:$R$607,"confidence_review")+COUNTIF('风光分项'!$R$2:$R$607,"待复核")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="14" t="n">
@@ -65896,7 +66405,7 @@
         <x:v>公众号与网站差异</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>2026-08-23两来源价格或电量存在口径差异</x:v>
+        <x:v>2026-08-29两来源价格或电量存在口径差异</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
         <x:v>同日数值不可直接混合</x:v>
@@ -65942,10 +66451,10 @@
         <x:v>风光分项披露</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>2025-04-06起公众号图片拆分风电与光伏；2025-11-16日报缺失</x:v>
+        <x:v>2025-04-06起公众号图片拆分风电与光伏；缺报日：2025-11-16、2026-08-24、2026-08-25</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>细分序列起点晚于总量序列且有1日空缺</x:v>
+        <x:v>细分序列起点晚于总量序列且有3日空缺</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
         <x:v>未披露区间和缺失日保留为空</x:v>
@@ -66116,7 +66625,7 @@
         <x:v>主数据源</x:v>
       </x:c>
       <x:c r="G6" s="15" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str">
         <x:v>公开结构化接口，每次返回近15日</x:v>
@@ -66142,10 +66651,10 @@
         <x:v>发布快照/交叉核验</x:v>
       </x:c>
       <x:c r="G7" s="15" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>已抓取504个风光分项披露日；部分明细为图片</x:v>
+        <x:v>已抓取508个风光分项披露日；部分明细为图片</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -66153,10 +66662,10 @@
         <x:v>S3</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>公众号-2026-08-23日报</x:v>
+        <x:v>公众号-2026-08-29日报</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508320&amp;idx=1&amp;sn=e713f1c01e8f55fb24b33a89441a7c91&amp;chksm=f9f995dace8e1ccc26339503680907736d4bba00b40149d311d4658dcc24ec0c865b95249c7b#rd</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508373&amp;idx=1&amp;sn=5775242f01351f95255fc9f692487e0a&amp;chksm=f9f9952fce8e1c39a0297087156ea17c215674d58075aa2b2cc1929653b3809fae91c95c45e3#rd</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
         <x:v>差异核验样本</x:v>
@@ -66168,10 +66677,10 @@
         <x:v>证据样本</x:v>
       </x:c>
       <x:c r="G8" s="15" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str">
-        <x:v>日前412.41、实时489.7元/MWh</x:v>
+        <x:v>日前172.48、实时188.04元/MWh</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -66194,7 +66703,7 @@
         <x:v>风光分项主数据源</x:v>
       </x:c>
       <x:c r="G9" s="15" t="n">
-        <x:v>46260</x:v>
+        <x:v>46265</x:v>
       </x:c>
       <x:c r="H9" s="14" t="str">
         <x:v>2025-04-06起披露；OCR提取，逐行保留原文链接与置信度</x:v>
@@ -66577,6 +67086,6 @@
     <x:mergeCell ref="A21:H21"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4bfc0389a7a409d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e7f27ffb6554db0"/>
 </x:worksheet>
 </file>
--- a/陕西现货市场每日出清价格跟踪_2025至今_含风光分项.xlsx
+++ b/陕西现货市场每日出清价格跟踪_2025至今_含风光分项.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R139c1d6da9fc40a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据" sheetId="2" r:id="R0962fd1e36764d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光分项" sheetId="3" r:id="R584b4fd2fb3047d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="4" r:id="Ra3f8ce54f72e4392"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光月度" sheetId="5" r:id="Rf013e8672d0f4814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量" sheetId="6" r:id="Rdd1a46fa2f4e4177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与跟踪计划" sheetId="7" r:id="Ra721e50686c140b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R44d4346b24134cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据" sheetId="2" r:id="Rb9f1e9690b314ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光分项" sheetId="3" r:id="Re74dfdbb96c34d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="4" r:id="R40e2aa896060415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风光月度" sheetId="5" r:id="R6aff1a3c70684336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量" sheetId="6" r:id="Re1276f3bf2384de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与跟踪计划" sheetId="7" r:id="R75a95867c2c8445b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={4EB2F4DF-DAD8-472D-A83B-66D96CC6C9BE}</x:author>
+    <x:author>tc={BA6CBAB1-ED4E-442F-83A6-A61275DC952C}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -25,7 +25,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    2026-08-29网站当前回溯值；抓取于2026-08-31。公众号同日快报用于核验，差异不覆盖网站主序列。</x:t>
+    2026-09-05网站当前回溯值；抓取于2026-09-07。公众号同日快报用于核验，差异不覆盖网站主序列。</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -36,7 +36,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={33BE459F-1A32-4F11-B54B-827CA68F48FA}</x:author>
+    <x:author>tc={26922523-EEF4-4024-B091-9B64D5DDAD36}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="C6" authorId="0">
@@ -388,7 +388,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'月度汇总'!$A$41:$A$60</c:f>
+              <c:f>'月度汇总'!$A$41:$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -396,7 +396,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'月度汇总'!$B$41:$B$60</c:f>
+              <c:f>'月度汇总'!$B$41:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -416,7 +416,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'月度汇总'!$A$41:$A$60</c:f>
+              <c:f>'月度汇总'!$A$41:$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -424,7 +424,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'月度汇总'!$C$41:$C$60</c:f>
+              <c:f>'月度汇总'!$C$41:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -542,7 +542,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'月度汇总'!$A$41:$A$60</c:f>
+              <c:f>'月度汇总'!$A$41:$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -550,7 +550,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'月度汇总'!$D$41:$D$60</c:f>
+              <c:f>'月度汇总'!$D$41:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -577,7 +577,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'月度汇总'!$A$41:$A$60</c:f>
+              <c:f>'月度汇总'!$A$41:$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -585,7 +585,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'月度汇总'!$E$41:$E$60</c:f>
+              <c:f>'月度汇总'!$E$41:$E$61</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -612,7 +612,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'月度汇总'!$A$41:$A$60</c:f>
+              <c:f>'月度汇总'!$A$41:$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -620,7 +620,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'月度汇总'!$F$41:$F$60</c:f>
+              <c:f>'月度汇总'!$F$41:$F$61</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -647,7 +647,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'月度汇总'!$A$41:$A$60</c:f>
+              <c:f>'月度汇总'!$A$41:$A$61</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -655,7 +655,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'月度汇总'!$G$41:$G$60</c:f>
+              <c:f>'月度汇总'!$G$41:$G$61</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -766,7 +766,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'风光月度'!$A$41:$A$57</c:f>
+              <c:f>'风光月度'!$A$41:$A$58</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -774,7 +774,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'风光月度'!$B$41:$B$57</c:f>
+              <c:f>'风光月度'!$B$41:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -794,7 +794,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'风光月度'!$A$41:$A$57</c:f>
+              <c:f>'风光月度'!$A$41:$A$58</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -802,7 +802,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'风光月度'!$C$41:$C$57</c:f>
+              <c:f>'风光月度'!$C$41:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -822,7 +822,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'风光月度'!$A$41:$A$57</c:f>
+              <c:f>'风光月度'!$A$41:$A$58</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -830,7 +830,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'风光月度'!$D$41:$D$57</c:f>
+              <c:f>'风光月度'!$D$41:$D$58</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -850,7 +850,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'风光月度'!$A$41:$A$57</c:f>
+              <c:f>'风光月度'!$A$41:$A$58</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -858,7 +858,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'风光月度'!$E$41:$E$57</c:f>
+              <c:f>'风光月度'!$E$41:$E$58</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -961,7 +961,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R968e07ba04594d22"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R33e4dd0b3b194019"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a726424902340ad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2fb73fa2c7864dbb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1026,7 +1026,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b1a95430feb4cf6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf913b38b47c346fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{44D13FE9-BE9F-430D-872C-E424BA039A0E}"/>
+  <xltc:person displayName="User" id="{F6A9DC57-8947-4EE5-8879-68EBAF5B8EF7}"/>
 </xltc:personList>
 </file>
 
@@ -1234,15 +1234,15 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-31T02:36:40.616" personId="{44D13FE9-BE9F-430D-872C-E424BA039A0E}" id="{4EB2F4DF-DAD8-472D-A83B-66D96CC6C9BE}">
-    <xltc:text>2026-08-29网站当前回溯值；抓取于2026-08-31。公众号同日快报用于核验，差异不覆盖网站主序列。</xltc:text>
+  <xltc:threadedComment ref="B18" dT="2026-09-07T02:37:24.195" personId="{F6A9DC57-8947-4EE5-8879-68EBAF5B8EF7}" id="{BA6CBAB1-ED4E-442F-83A6-A61275DC952C}">
+    <xltc:text>2026-09-05网站当前回溯值；抓取于2026-09-07。公众号同日快报用于核验，差异不覆盖网站主序列。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
 
 <file path=xl/threadedcomments/threadedcomment2.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="C6" dT="2026-08-31T02:36:40.616" personId="{44D13FE9-BE9F-430D-872C-E424BA039A0E}" id="{33BE459F-1A32-4F11-B54B-827CA68F48FA}">
+  <xltc:threadedComment ref="C6" dT="2026-09-07T02:37:24.195" personId="{F6A9DC57-8947-4EE5-8879-68EBAF5B8EF7}" id="{26922523-EEF4-4024-B091-9B64D5DDAD36}">
     <xltc:text>主数据来自陕西电力交易中心现货专区公开接口；工作簿内保留网页入口便于人工复核。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1290,28 +1290,28 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="D2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="E2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="F2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="G2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
       <x:c r="H2" s="28" t="str">
-        <x:v>回溯区间：2025-01-01 至 2026-08-29｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
+        <x:v>回溯区间：2025-01-01 至 2026-09-05｜单位：元/兆瓦时；电量为兆瓦时｜数据源：陕西电力交易中心公开市场数据与微信公众号日报</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1355,8 +1355,8 @@
         <x:v>完整日期数</x:v>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTA('每日数据'!$A$2:$A$607)</x:f>
-        <x:v>606</x:v>
+        <x:f>COUNTA('每日数据'!$A$2:$A$614)</x:f>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="C5" s="29"/>
       <x:c r="D5" s="29"/>
@@ -1370,8 +1370,8 @@
         <x:v>最新完整披露日</x:v>
       </x:c>
       <x:c r="B6" s="33" t="n">
-        <x:f>MAX('每日数据'!$A$2:$A$607)</x:f>
-        <x:v>46263</x:v>
+        <x:f>MAX('每日数据'!$A$2:$A$614)</x:f>
+        <x:v>46270</x:v>
       </x:c>
       <x:c r="C6" s="29"/>
       <x:c r="D6" s="29"/>
@@ -1385,8 +1385,8 @@
         <x:v>最新日前 / 实时均价</x:v>
       </x:c>
       <x:c r="B7" s="32" t="str">
-        <x:f>INDEX('每日数据'!$B$2:$B$607,MATCH(B6,'每日数据'!$A$2:$A$607,0))&amp;" / "&amp;INDEX('每日数据'!$C$2:$C$607,MATCH(B6,'每日数据'!$A$2:$A$607,0))</x:f>
-        <x:v>172.48 / 188.04</x:v>
+        <x:f>INDEX('每日数据'!$B$2:$B$614,MATCH(B6,'每日数据'!$A$2:$A$614,0))&amp;" / "&amp;INDEX('每日数据'!$C$2:$C$614,MATCH(B6,'每日数据'!$A$2:$A$614,0))</x:f>
+        <x:v>229.57 / 323.18</x:v>
       </x:c>
       <x:c r="C7" s="29"/>
       <x:c r="D7" s="29"/>
@@ -1549,28 +1549,28 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="B16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="C16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="D16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="E16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="F16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="G16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
       <x:c r="H16" s="30" t="str">
-        <x:v>口径差异示例（2026-08-29）</x:v>
+        <x:v>口径差异示例（2026-09-05）</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -1598,16 +1598,16 @@
         <x:v>网站当前回溯接口</x:v>
       </x:c>
       <x:c r="B18" s="37" t="n">
-        <x:v>172.48</x:v>
+        <x:v>229.57</x:v>
       </x:c>
       <x:c r="C18" s="37" t="n">
-        <x:v>188.04</x:v>
+        <x:v>323.18</x:v>
       </x:c>
       <x:c r="D18" s="37" t="n">
-        <x:v>213.816904</x:v>
+        <x:v>180.195184</x:v>
       </x:c>
       <x:c r="E18" s="37" t="n">
-        <x:v>216.09009500000002</x:v>
+        <x:v>204.099205</x:v>
       </x:c>
       <x:c r="F18" s="29"/>
       <x:c r="G18" s="29"/>
@@ -1618,16 +1618,16 @@
         <x:v>公众号次日日报</x:v>
       </x:c>
       <x:c r="B19" s="37" t="n">
-        <x:v>172.48</x:v>
+        <x:v>229.57</x:v>
       </x:c>
       <x:c r="C19" s="37" t="n">
-        <x:v>188.04</x:v>
+        <x:v>323.18</x:v>
       </x:c>
       <x:c r="D19" s="37" t="n">
-        <x:v>53.5</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E19" s="37" t="n">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F19" s="29"/>
       <x:c r="G19" s="29"/>
@@ -1820,7 +1820,7 @@
     <x:mergeCell ref="A24:H24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R210b7f5b496d49b8"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R208834dd5d744c4b"/>
 </x:worksheet>
 </file>
 
@@ -1932,7 +1932,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N2" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1979,7 +1979,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N3" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2026,7 +2026,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N4" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2073,7 +2073,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N5" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2120,7 +2120,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N6" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2167,7 +2167,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N7" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2214,7 +2214,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N8" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2261,7 +2261,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N9" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2308,7 +2308,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N10" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2355,7 +2355,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N11" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2402,7 +2402,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N12" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2449,7 +2449,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N13" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2496,7 +2496,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N14" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2543,7 +2543,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N15" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2590,7 +2590,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N16" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2637,7 +2637,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N17" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2684,7 +2684,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N18" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2731,7 +2731,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N19" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2778,7 +2778,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N20" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2825,7 +2825,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N21" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2872,7 +2872,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N22" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2919,7 +2919,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N23" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2966,7 +2966,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N24" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3013,7 +3013,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N25" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3060,7 +3060,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N26" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3107,7 +3107,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N27" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3154,7 +3154,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N28" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3201,7 +3201,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N29" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3248,7 +3248,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N30" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3295,7 +3295,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N31" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3342,7 +3342,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N32" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3389,7 +3389,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N33" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3436,7 +3436,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N34" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3483,7 +3483,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N35" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3530,7 +3530,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N36" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3577,7 +3577,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N37" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3624,7 +3624,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N38" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3671,7 +3671,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N39" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3718,7 +3718,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N40" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3765,7 +3765,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N41" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3812,7 +3812,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N42" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3859,7 +3859,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N43" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3906,7 +3906,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N44" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3953,7 +3953,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N45" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4000,7 +4000,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N46" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4047,7 +4047,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N47" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4094,7 +4094,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N48" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4141,7 +4141,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N49" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4188,7 +4188,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N50" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4235,7 +4235,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N51" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -4282,7 +4282,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N52" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -4329,7 +4329,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N53" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -4376,7 +4376,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N54" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -4423,7 +4423,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N55" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -4470,7 +4470,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N56" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -4517,7 +4517,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N57" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -4564,7 +4564,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N58" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -4611,7 +4611,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N59" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -4658,7 +4658,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N60" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -4705,7 +4705,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N61" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -4752,7 +4752,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N62" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -4799,7 +4799,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N63" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -4846,7 +4846,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N64" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -4893,7 +4893,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N65" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -4940,7 +4940,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N66" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -4987,7 +4987,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N67" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -5034,7 +5034,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N68" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -5081,7 +5081,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N69" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -5128,7 +5128,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N70" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -5175,7 +5175,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N71" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -5222,7 +5222,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N72" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -5269,7 +5269,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N73" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -5316,7 +5316,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N74" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -5363,7 +5363,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N75" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -5410,7 +5410,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N76" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -5457,7 +5457,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N77" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -5504,7 +5504,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N78" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -5551,7 +5551,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N79" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -5598,7 +5598,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N80" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -5645,7 +5645,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N81" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -5692,7 +5692,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N82" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -5739,7 +5739,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N83" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -5786,7 +5786,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N84" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -5833,7 +5833,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N85" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -5880,7 +5880,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N86" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -5927,7 +5927,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N87" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -5974,7 +5974,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N88" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -6021,7 +6021,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N89" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -6068,7 +6068,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N90" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -6115,7 +6115,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N91" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -6162,7 +6162,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N92" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -6209,7 +6209,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N93" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -6256,7 +6256,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N94" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -6303,7 +6303,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N95" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -6350,7 +6350,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N96" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -6397,7 +6397,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N97" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -6444,7 +6444,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N98" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -6491,7 +6491,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N99" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -6538,7 +6538,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N100" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -6585,7 +6585,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N101" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -6632,7 +6632,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N102" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -6679,7 +6679,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N103" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -6726,7 +6726,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N104" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -6773,7 +6773,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N105" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -6820,7 +6820,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N106" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -6867,7 +6867,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N107" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -6914,7 +6914,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N108" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -6961,7 +6961,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N109" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -7008,7 +7008,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N110" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -7055,7 +7055,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N111" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -7102,7 +7102,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N112" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7149,7 +7149,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N113" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -7196,7 +7196,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N114" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -7243,7 +7243,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N115" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -7290,7 +7290,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N116" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -7337,7 +7337,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N117" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -7384,7 +7384,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N118" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -7431,7 +7431,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N119" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -7478,7 +7478,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N120" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -7525,7 +7525,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N121" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -7572,7 +7572,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N122" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -7619,7 +7619,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N123" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -7666,7 +7666,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N124" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -7713,7 +7713,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N125" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -7760,7 +7760,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N126" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -7807,7 +7807,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N127" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -7854,7 +7854,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N128" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -7901,7 +7901,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N129" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -7948,7 +7948,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N130" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -7995,7 +7995,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N131" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -8042,7 +8042,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N132" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -8089,7 +8089,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N133" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -8136,7 +8136,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N134" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -8183,7 +8183,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N135" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -8230,7 +8230,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N136" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -8277,7 +8277,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N137" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -8324,7 +8324,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N138" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -8371,7 +8371,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N139" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -8418,7 +8418,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N140" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -8465,7 +8465,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N141" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -8512,7 +8512,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N142" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -8559,7 +8559,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N143" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -8606,7 +8606,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N144" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -8653,7 +8653,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N145" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -8700,7 +8700,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N146" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -8747,7 +8747,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N147" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -8794,7 +8794,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N148" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -8841,7 +8841,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N149" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -8888,7 +8888,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N150" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -8935,7 +8935,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N151" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -8982,7 +8982,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N152" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -9029,7 +9029,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N153" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -9076,7 +9076,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N154" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -9123,7 +9123,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N155" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -9170,7 +9170,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N156" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -9217,7 +9217,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N157" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -9264,7 +9264,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N158" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -9311,7 +9311,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N159" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -9358,7 +9358,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N160" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -9405,7 +9405,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N161" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -9452,7 +9452,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N162" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -9499,7 +9499,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N163" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -9546,7 +9546,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N164" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -9593,7 +9593,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N165" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -9640,7 +9640,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N166" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -9687,7 +9687,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N167" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -9734,7 +9734,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N168" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -9781,7 +9781,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N169" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -9828,7 +9828,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N170" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -9875,7 +9875,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N171" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -9922,7 +9922,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N172" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -9969,7 +9969,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N173" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -10016,7 +10016,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N174" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -10063,7 +10063,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N175" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -10110,7 +10110,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N176" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -10157,7 +10157,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N177" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -10198,7 +10198,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N178" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -10245,7 +10245,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N179" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -10292,7 +10292,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N180" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -10339,7 +10339,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N181" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -10386,7 +10386,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N182" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -10433,7 +10433,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N183" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -10480,7 +10480,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N184" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -10527,7 +10527,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N185" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -10574,7 +10574,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N186" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -10621,7 +10621,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N187" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -10668,7 +10668,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N188" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -10715,7 +10715,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N189" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -10762,7 +10762,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N190" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -10809,7 +10809,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N191" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -10856,7 +10856,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N192" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -10903,7 +10903,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N193" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -10950,7 +10950,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N194" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -10997,7 +10997,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N195" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -11044,7 +11044,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N196" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -11091,7 +11091,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N197" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -11138,7 +11138,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N198" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -11185,7 +11185,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N199" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -11232,7 +11232,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N200" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -11279,7 +11279,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N201" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -11326,7 +11326,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N202" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -11373,7 +11373,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N203" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -11420,7 +11420,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N204" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -11467,7 +11467,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N205" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -11514,7 +11514,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N206" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -11561,7 +11561,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N207" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -11608,7 +11608,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N208" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -11655,7 +11655,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N209" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -11702,7 +11702,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N210" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -11749,7 +11749,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N211" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -11796,7 +11796,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N212" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -11843,7 +11843,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N213" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -11890,7 +11890,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N214" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -11937,7 +11937,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N215" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -11984,7 +11984,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N216" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -12031,7 +12031,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N217" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -12078,7 +12078,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N218" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -12125,7 +12125,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N219" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -12172,7 +12172,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N220" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -12219,7 +12219,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N221" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -12266,7 +12266,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N222" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -12313,7 +12313,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N223" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -12360,7 +12360,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N224" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -12407,7 +12407,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N225" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -12454,7 +12454,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N226" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -12501,7 +12501,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N227" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -12548,7 +12548,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N228" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -12595,7 +12595,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N229" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -12642,7 +12642,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N230" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -12689,7 +12689,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N231" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -12736,7 +12736,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N232" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -12783,7 +12783,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N233" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -12830,7 +12830,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N234" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -12877,7 +12877,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N235" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -12924,7 +12924,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N236" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -12971,7 +12971,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N237" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -13018,7 +13018,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N238" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -13065,7 +13065,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N239" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -13112,7 +13112,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N240" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -13159,7 +13159,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N241" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -13206,7 +13206,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N242" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -13253,7 +13253,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N243" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -13300,7 +13300,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N244" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -13347,7 +13347,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N245" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -13394,7 +13394,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N246" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
@@ -13441,7 +13441,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N247" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -13488,7 +13488,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N248" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
@@ -13535,7 +13535,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N249" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -13582,7 +13582,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N250" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -13629,7 +13629,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N251" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -13676,7 +13676,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N252" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -13723,7 +13723,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N253" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -13770,7 +13770,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N254" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -13817,7 +13817,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N255" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -13864,7 +13864,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N256" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -13911,7 +13911,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N257" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -13958,7 +13958,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N258" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -14005,7 +14005,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N259" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -14052,7 +14052,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N260" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
@@ -14099,7 +14099,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N261" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -14146,7 +14146,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N262" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="263">
@@ -14193,7 +14193,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N263" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -14240,7 +14240,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N264" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
@@ -14287,7 +14287,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N265" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
@@ -14334,7 +14334,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N266" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
@@ -14381,7 +14381,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N267" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -14428,7 +14428,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N268" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
@@ -14475,7 +14475,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N269" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -14522,7 +14522,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N270" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -14569,7 +14569,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N271" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -14616,7 +14616,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N272" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
@@ -14663,7 +14663,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N273" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -14710,7 +14710,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N274" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -14757,7 +14757,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N275" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -14804,7 +14804,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N276" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
@@ -14851,7 +14851,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N277" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -14898,7 +14898,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N278" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -14945,7 +14945,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N279" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -14992,7 +14992,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N280" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -15039,7 +15039,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N281" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -15086,7 +15086,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N282" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -15133,7 +15133,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N283" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -15180,7 +15180,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N284" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -15227,7 +15227,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N285" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -15274,7 +15274,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N286" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -15321,7 +15321,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N287" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -15368,7 +15368,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N288" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -15415,7 +15415,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N289" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -15462,7 +15462,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N290" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -15509,7 +15509,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N291" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -15556,7 +15556,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N292" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -15603,7 +15603,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N293" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -15650,7 +15650,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N294" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="295">
@@ -15697,7 +15697,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N295" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -15744,7 +15744,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N296" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -15791,7 +15791,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N297" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
@@ -15838,7 +15838,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N298" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
@@ -15885,7 +15885,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N299" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
@@ -15932,7 +15932,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N300" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -15979,7 +15979,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N301" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
@@ -16026,7 +16026,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N302" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -16073,7 +16073,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N303" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -16120,7 +16120,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N304" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
@@ -16167,7 +16167,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N305" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -16214,7 +16214,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N306" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -16261,7 +16261,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N307" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
@@ -16308,7 +16308,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N308" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -16355,7 +16355,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N309" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -16402,7 +16402,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N310" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -16449,7 +16449,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N311" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
@@ -16496,7 +16496,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N312" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
@@ -16543,7 +16543,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N313" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="314">
@@ -16590,7 +16590,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N314" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -16637,7 +16637,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N315" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="316">
@@ -16684,7 +16684,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N316" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
@@ -16731,7 +16731,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N317" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
@@ -16778,7 +16778,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N318" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -16825,7 +16825,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N319" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -16872,7 +16872,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N320" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
@@ -16919,7 +16919,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N321" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
@@ -16966,7 +16966,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N322" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="323">
@@ -17013,7 +17013,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N323" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -17060,7 +17060,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N324" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -17107,7 +17107,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N325" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -17154,7 +17154,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N326" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
@@ -17201,7 +17201,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N327" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -17248,7 +17248,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N328" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
@@ -17295,7 +17295,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N329" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="330">
@@ -17342,7 +17342,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N330" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="331">
@@ -17389,7 +17389,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N331" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
@@ -17436,7 +17436,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N332" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="333">
@@ -17483,7 +17483,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N333" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="334">
@@ -17530,7 +17530,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N334" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -17577,7 +17577,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N335" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -17624,7 +17624,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N336" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
@@ -17671,7 +17671,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N337" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="338">
@@ -17718,7 +17718,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N338" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -17765,7 +17765,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N339" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
@@ -17812,7 +17812,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N340" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -17859,7 +17859,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N341" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
@@ -17906,7 +17906,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N342" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
@@ -17953,7 +17953,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N343" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -18000,7 +18000,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N344" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="345">
@@ -18047,7 +18047,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N345" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="346">
@@ -18094,7 +18094,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N346" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="347">
@@ -18141,7 +18141,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N347" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
@@ -18188,7 +18188,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N348" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -18235,7 +18235,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N349" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="350">
@@ -18282,7 +18282,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N350" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -18329,7 +18329,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N351" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -18376,7 +18376,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N352" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
@@ -18423,7 +18423,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N353" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="354">
@@ -18470,7 +18470,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N354" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -18517,7 +18517,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N355" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -18564,7 +18564,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N356" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -18611,7 +18611,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N357" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -18658,7 +18658,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N358" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="359">
@@ -18705,7 +18705,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N359" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -18752,7 +18752,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N360" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="361">
@@ -18799,7 +18799,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N361" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="362">
@@ -18846,7 +18846,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N362" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -18893,7 +18893,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N363" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -18940,7 +18940,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N364" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -18987,7 +18987,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N365" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="366">
@@ -19034,7 +19034,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N366" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="367">
@@ -19081,7 +19081,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N367" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="368">
@@ -19128,7 +19128,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N368" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="369">
@@ -19175,7 +19175,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N369" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
@@ -19222,7 +19222,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N370" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -19269,7 +19269,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N371" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -19316,7 +19316,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N372" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="373">
@@ -19363,7 +19363,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N373" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -19410,7 +19410,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N374" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -19457,7 +19457,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N375" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -19504,7 +19504,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N376" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
@@ -19551,7 +19551,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N377" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
@@ -19598,7 +19598,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N378" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -19645,7 +19645,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N379" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -19692,7 +19692,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N380" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -19739,7 +19739,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N381" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="382">
@@ -19786,7 +19786,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N382" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -19833,7 +19833,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N383" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="384">
@@ -19880,7 +19880,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N384" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -19927,7 +19927,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N385" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -19974,7 +19974,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N386" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="387">
@@ -20021,7 +20021,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N387" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -20068,7 +20068,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N388" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="389">
@@ -20115,7 +20115,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N389" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="390">
@@ -20162,7 +20162,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N390" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -20209,7 +20209,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N391" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -20256,7 +20256,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N392" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -20303,7 +20303,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N393" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
@@ -20350,7 +20350,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N394" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -20397,7 +20397,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N395" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="396">
@@ -20444,7 +20444,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N396" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="397">
@@ -20491,7 +20491,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N397" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -20538,7 +20538,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N398" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
@@ -20585,7 +20585,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N399" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
@@ -20632,7 +20632,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N400" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
@@ -20679,7 +20679,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N401" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="402">
@@ -20726,7 +20726,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N402" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="403">
@@ -20773,7 +20773,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N403" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="404">
@@ -20820,7 +20820,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N404" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="405">
@@ -20867,7 +20867,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N405" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -20914,7 +20914,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N406" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -20961,7 +20961,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N407" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
@@ -21008,7 +21008,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N408" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="409">
@@ -21055,7 +21055,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N409" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
@@ -21102,7 +21102,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N410" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="411">
@@ -21149,7 +21149,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N411" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="412">
@@ -21196,7 +21196,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N412" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="413">
@@ -21243,7 +21243,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N413" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="414">
@@ -21290,7 +21290,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N414" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="415">
@@ -21337,7 +21337,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N415" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="416">
@@ -21384,7 +21384,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N416" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="417">
@@ -21431,7 +21431,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N417" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -21478,7 +21478,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N418" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="419">
@@ -21525,7 +21525,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N419" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="420">
@@ -21572,7 +21572,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N420" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -21619,7 +21619,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N421" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -21666,7 +21666,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N422" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="423">
@@ -21713,7 +21713,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N423" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="424">
@@ -21760,7 +21760,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N424" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -21807,7 +21807,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N425" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -21854,7 +21854,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N426" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -21901,7 +21901,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N427" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -21948,7 +21948,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N428" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="429">
@@ -21995,7 +21995,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N429" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -22042,7 +22042,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N430" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -22089,7 +22089,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N431" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="432">
@@ -22136,7 +22136,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N432" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -22183,7 +22183,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N433" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -22230,7 +22230,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N434" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -22277,7 +22277,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N435" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -22324,7 +22324,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N436" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -22371,7 +22371,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N437" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="438">
@@ -22418,7 +22418,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N438" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -22465,7 +22465,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N439" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -22512,7 +22512,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N440" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="441">
@@ -22559,7 +22559,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N441" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -22606,7 +22606,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N442" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="443">
@@ -22653,7 +22653,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N443" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="444">
@@ -22700,7 +22700,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N444" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="445">
@@ -22747,7 +22747,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N445" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="446">
@@ -22794,7 +22794,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N446" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="447">
@@ -22841,7 +22841,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N447" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
@@ -22888,7 +22888,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N448" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -22935,7 +22935,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N449" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
@@ -22982,7 +22982,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N450" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -23029,7 +23029,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N451" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
@@ -23076,7 +23076,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N452" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
@@ -23123,7 +23123,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N453" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
@@ -23170,7 +23170,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N454" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
@@ -23217,7 +23217,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N455" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -23264,7 +23264,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N456" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -23311,7 +23311,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N457" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
@@ -23358,7 +23358,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N458" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
@@ -23405,7 +23405,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N459" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
@@ -23452,7 +23452,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N460" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
@@ -23499,7 +23499,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N461" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
@@ -23546,7 +23546,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N462" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -23593,7 +23593,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N463" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
@@ -23640,7 +23640,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N464" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -23687,7 +23687,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N465" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -23734,7 +23734,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N466" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -23781,7 +23781,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N467" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="468">
@@ -23828,7 +23828,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N468" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -23875,7 +23875,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N469" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -23922,7 +23922,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N470" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -23969,7 +23969,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N471" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -24016,7 +24016,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N472" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -24063,7 +24063,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N473" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="474">
@@ -24110,7 +24110,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N474" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -24157,7 +24157,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N475" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
@@ -24204,7 +24204,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N476" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -24251,7 +24251,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N477" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
@@ -24298,7 +24298,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N478" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -24345,7 +24345,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N479" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
@@ -24392,7 +24392,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N480" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -24439,7 +24439,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N481" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -24486,7 +24486,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N482" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -24533,7 +24533,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N483" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
@@ -24580,7 +24580,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N484" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -24627,7 +24627,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N485" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -24674,7 +24674,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N486" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -24721,7 +24721,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N487" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -24768,7 +24768,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N488" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
@@ -24815,7 +24815,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N489" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -24862,7 +24862,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N490" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -24909,7 +24909,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N491" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -24956,7 +24956,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N492" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -25003,7 +25003,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N493" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="494">
@@ -25050,7 +25050,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N494" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -25097,7 +25097,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N495" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
@@ -25144,7 +25144,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N496" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -25191,7 +25191,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N497" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -25238,7 +25238,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N498" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -25285,7 +25285,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N499" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -25332,7 +25332,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N500" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -25379,7 +25379,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N501" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
@@ -25426,7 +25426,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N502" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -25473,7 +25473,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N503" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
@@ -25520,7 +25520,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N504" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -25567,7 +25567,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N505" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="506">
@@ -25614,7 +25614,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N506" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -25661,7 +25661,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N507" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
@@ -25708,7 +25708,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N508" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -25755,7 +25755,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N509" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
@@ -25802,7 +25802,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N510" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -25849,7 +25849,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N511" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
@@ -25896,7 +25896,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N512" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -25943,7 +25943,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N513" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -25990,7 +25990,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N514" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -26037,7 +26037,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N515" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="516">
@@ -26084,7 +26084,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N516" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -26131,7 +26131,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N517" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
@@ -26178,7 +26178,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N518" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -26225,7 +26225,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N519" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -26272,7 +26272,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N520" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -26319,7 +26319,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N521" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="522">
@@ -26366,7 +26366,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N522" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -26413,7 +26413,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N523" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="524">
@@ -26460,7 +26460,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N524" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -26507,7 +26507,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N525" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
@@ -26554,7 +26554,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N526" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -26601,7 +26601,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N527" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
@@ -26648,7 +26648,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N528" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -26695,7 +26695,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N529" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
@@ -26742,7 +26742,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N530" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -26789,7 +26789,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N531" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -26836,7 +26836,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N532" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
@@ -26883,7 +26883,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N533" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="534">
@@ -26930,7 +26930,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N534" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -26977,7 +26977,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N535" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
@@ -27024,7 +27024,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N536" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
@@ -27071,7 +27071,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N537" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="538">
@@ -27118,7 +27118,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N538" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="539">
@@ -27165,7 +27165,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N539" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="540">
@@ -27212,7 +27212,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N540" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="541">
@@ -27259,7 +27259,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N541" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="542">
@@ -27306,7 +27306,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N542" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="543">
@@ -27353,7 +27353,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N543" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="544">
@@ -27400,7 +27400,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N544" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="545">
@@ -27447,7 +27447,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N545" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="546">
@@ -27494,7 +27494,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N546" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="547">
@@ -27541,7 +27541,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N547" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="548">
@@ -27588,7 +27588,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N548" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="549">
@@ -27635,7 +27635,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N549" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="550">
@@ -27682,7 +27682,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N550" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="551">
@@ -27729,7 +27729,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N551" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="552">
@@ -27776,7 +27776,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N552" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="553">
@@ -27823,7 +27823,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N553" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="554">
@@ -27870,7 +27870,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N554" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="555">
@@ -27917,7 +27917,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N555" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="556">
@@ -27964,7 +27964,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N556" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="557">
@@ -28011,7 +28011,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N557" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="558">
@@ -28058,7 +28058,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N558" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="559">
@@ -28105,7 +28105,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N559" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="560">
@@ -28152,7 +28152,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N560" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="561">
@@ -28191,7 +28191,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N561" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="562">
@@ -28238,7 +28238,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N562" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="563">
@@ -28285,7 +28285,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N563" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="564">
@@ -28332,7 +28332,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N564" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="565">
@@ -28379,7 +28379,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N565" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="566">
@@ -28426,7 +28426,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N566" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="567">
@@ -28473,7 +28473,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N567" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="568">
@@ -28520,7 +28520,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N568" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="569">
@@ -28567,7 +28567,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N569" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="570">
@@ -28614,7 +28614,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N570" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="571">
@@ -28661,7 +28661,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N571" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="572">
@@ -28708,7 +28708,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N572" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="573">
@@ -28755,7 +28755,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N573" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="574">
@@ -28802,7 +28802,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N574" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="575">
@@ -28849,7 +28849,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N575" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="576">
@@ -28896,7 +28896,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N576" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="577">
@@ -28943,7 +28943,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N577" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="578">
@@ -28990,7 +28990,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N578" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="579">
@@ -29037,7 +29037,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N579" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="580">
@@ -29084,7 +29084,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N580" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="581">
@@ -29131,7 +29131,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N581" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="582">
@@ -29178,7 +29178,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N582" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="583">
@@ -29225,7 +29225,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N583" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="584">
@@ -29272,7 +29272,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N584" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="585">
@@ -29319,7 +29319,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N585" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="586">
@@ -29366,7 +29366,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N586" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="587">
@@ -29413,7 +29413,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N587" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="588">
@@ -29460,7 +29460,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N588" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="589">
@@ -29507,7 +29507,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N589" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="590">
@@ -29554,7 +29554,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N590" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="591">
@@ -29601,7 +29601,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N591" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="592">
@@ -29648,7 +29648,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N592" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="593">
@@ -29695,7 +29695,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N593" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="594">
@@ -29742,7 +29742,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N594" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="595">
@@ -29789,7 +29789,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N595" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="596">
@@ -29836,7 +29836,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N596" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="597">
@@ -29883,7 +29883,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N597" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="598">
@@ -29930,7 +29930,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N598" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="599">
@@ -29977,7 +29977,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N599" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="600">
@@ -30024,7 +30024,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N600" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="601">
@@ -30071,7 +30071,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N601" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="602">
@@ -30118,7 +30118,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N602" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="603">
@@ -30165,7 +30165,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N603" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="604">
@@ -30212,7 +30212,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N604" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="605">
@@ -30259,7 +30259,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N605" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="606">
@@ -30306,7 +30306,7 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N606" s="41" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="607">
@@ -30353,7 +30353,336 @@
         <x:v>网站结构化接口</x:v>
       </x:c>
       <x:c r="N607" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608">
+      <x:c r="A608" s="41" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="B608" s="42" t="n">
+        <x:v>263.65</x:v>
+      </x:c>
+      <x:c r="C608" s="42" t="n">
+        <x:v>252.58</x:v>
+      </x:c>
+      <x:c r="D608" s="42" t="n">
+        <x:v>310.05</x:v>
+      </x:c>
+      <x:c r="E608" s="42" t="n">
+        <x:v>297.22</x:v>
+      </x:c>
+      <x:c r="F608" s="42" t="n">
+        <x:v>70.36</x:v>
+      </x:c>
+      <x:c r="G608" s="42" t="n">
+        <x:v>74.35</x:v>
+      </x:c>
+      <x:c r="H608" s="43" t="n">
+        <x:v>2148865.26</x:v>
+      </x:c>
+      <x:c r="I608" s="43" t="n">
+        <x:v>2154616.58</x:v>
+      </x:c>
+      <x:c r="J608" s="42" t="n">
+        <x:f>B608-C608</x:f>
+        <x:v>11.069999999999965</x:v>
+      </x:c>
+      <x:c r="K608" s="42" t="n">
+        <x:f>D608-F608</x:f>
+        <x:v>239.69</x:v>
+      </x:c>
+      <x:c r="L608" s="42" t="n">
+        <x:f>E608-G608</x:f>
+        <x:v>222.87000000000003</x:v>
+      </x:c>
+      <x:c r="M608" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N608" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609">
+      <x:c r="A609" s="41" t="n">
         <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B609" s="42" t="n">
+        <x:v>236.93</x:v>
+      </x:c>
+      <x:c r="C609" s="42" t="n">
+        <x:v>199.42</x:v>
+      </x:c>
+      <x:c r="D609" s="42" t="n">
+        <x:v>278.63</x:v>
+      </x:c>
+      <x:c r="E609" s="42" t="n">
+        <x:v>236.95</x:v>
+      </x:c>
+      <x:c r="F609" s="42" t="n">
+        <x:v>82.94</x:v>
+      </x:c>
+      <x:c r="G609" s="42" t="n">
+        <x:v>74.1</x:v>
+      </x:c>
+      <x:c r="H609" s="43" t="n">
+        <x:v>2129993.68</x:v>
+      </x:c>
+      <x:c r="I609" s="43" t="n">
+        <x:v>2077173.26</x:v>
+      </x:c>
+      <x:c r="J609" s="42" t="n">
+        <x:f>B609-C609</x:f>
+        <x:v>37.51000000000002</x:v>
+      </x:c>
+      <x:c r="K609" s="42" t="n">
+        <x:f>D609-F609</x:f>
+        <x:v>195.69</x:v>
+      </x:c>
+      <x:c r="L609" s="42" t="n">
+        <x:f>E609-G609</x:f>
+        <x:v>162.85</x:v>
+      </x:c>
+      <x:c r="M609" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N609" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610">
+      <x:c r="A610" s="41" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B610" s="42" t="n">
+        <x:v>246.3</x:v>
+      </x:c>
+      <x:c r="C610" s="42" t="n">
+        <x:v>220.47</x:v>
+      </x:c>
+      <x:c r="D610" s="42" t="n">
+        <x:v>297.45</x:v>
+      </x:c>
+      <x:c r="E610" s="42" t="n">
+        <x:v>268.11</x:v>
+      </x:c>
+      <x:c r="F610" s="42" t="n">
+        <x:v>128.17</x:v>
+      </x:c>
+      <x:c r="G610" s="42" t="n">
+        <x:v>115.73</x:v>
+      </x:c>
+      <x:c r="H610" s="43" t="n">
+        <x:v>2080974.4</x:v>
+      </x:c>
+      <x:c r="I610" s="43" t="n">
+        <x:v>2002859.94</x:v>
+      </x:c>
+      <x:c r="J610" s="42" t="n">
+        <x:f>B610-C610</x:f>
+        <x:v>25.830000000000013</x:v>
+      </x:c>
+      <x:c r="K610" s="42" t="n">
+        <x:f>D610-F610</x:f>
+        <x:v>169.28</x:v>
+      </x:c>
+      <x:c r="L610" s="42" t="n">
+        <x:f>E610-G610</x:f>
+        <x:v>152.38</x:v>
+      </x:c>
+      <x:c r="M610" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N610" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611">
+      <x:c r="A611" s="41" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="B611" s="42" t="n">
+        <x:v>210.62</x:v>
+      </x:c>
+      <x:c r="C611" s="42" t="n">
+        <x:v>222.19</x:v>
+      </x:c>
+      <x:c r="D611" s="42" t="n">
+        <x:v>254.65</x:v>
+      </x:c>
+      <x:c r="E611" s="42" t="n">
+        <x:v>262.54</x:v>
+      </x:c>
+      <x:c r="F611" s="42" t="n">
+        <x:v>138.78</x:v>
+      </x:c>
+      <x:c r="G611" s="42" t="n">
+        <x:v>162.94</x:v>
+      </x:c>
+      <x:c r="H611" s="43" t="n">
+        <x:v>1973001.6</x:v>
+      </x:c>
+      <x:c r="I611" s="43" t="n">
+        <x:v>1994925.91</x:v>
+      </x:c>
+      <x:c r="J611" s="42" t="n">
+        <x:f>B611-C611</x:f>
+        <x:v>-11.569999999999993</x:v>
+      </x:c>
+      <x:c r="K611" s="42" t="n">
+        <x:f>D611-F611</x:f>
+        <x:v>115.87</x:v>
+      </x:c>
+      <x:c r="L611" s="42" t="n">
+        <x:f>E611-G611</x:f>
+        <x:v>99.60000000000002</x:v>
+      </x:c>
+      <x:c r="M611" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N611" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612">
+      <x:c r="A612" s="41" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="B612" s="42" t="n">
+        <x:v>208.75</x:v>
+      </x:c>
+      <x:c r="C612" s="42" t="n">
+        <x:v>218.69</x:v>
+      </x:c>
+      <x:c r="D612" s="42" t="n">
+        <x:v>256.97</x:v>
+      </x:c>
+      <x:c r="E612" s="42" t="n">
+        <x:v>252.31</x:v>
+      </x:c>
+      <x:c r="F612" s="42" t="n">
+        <x:v>140.22</x:v>
+      </x:c>
+      <x:c r="G612" s="42" t="n">
+        <x:v>170.75</x:v>
+      </x:c>
+      <x:c r="H612" s="43" t="n">
+        <x:v>1896583.97</x:v>
+      </x:c>
+      <x:c r="I612" s="43" t="n">
+        <x:v>1891148.92</x:v>
+      </x:c>
+      <x:c r="J612" s="42" t="n">
+        <x:f>B612-C612</x:f>
+        <x:v>-9.939999999999998</x:v>
+      </x:c>
+      <x:c r="K612" s="42" t="n">
+        <x:f>D612-F612</x:f>
+        <x:v>116.75000000000003</x:v>
+      </x:c>
+      <x:c r="L612" s="42" t="n">
+        <x:f>E612-G612</x:f>
+        <x:v>81.56</x:v>
+      </x:c>
+      <x:c r="M612" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N612" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613">
+      <x:c r="A613" s="41" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="B613" s="42" t="n">
+        <x:v>228.92</x:v>
+      </x:c>
+      <x:c r="C613" s="42" t="n">
+        <x:v>346.76</x:v>
+      </x:c>
+      <x:c r="D613" s="42" t="n">
+        <x:v>274.85</x:v>
+      </x:c>
+      <x:c r="E613" s="42" t="n">
+        <x:v>425.56</x:v>
+      </x:c>
+      <x:c r="F613" s="42" t="n">
+        <x:v>150.48</x:v>
+      </x:c>
+      <x:c r="G613" s="42" t="n">
+        <x:v>196.87</x:v>
+      </x:c>
+      <x:c r="H613" s="43" t="n">
+        <x:v>1906658.05</x:v>
+      </x:c>
+      <x:c r="I613" s="43" t="n">
+        <x:v>1967781.95</x:v>
+      </x:c>
+      <x:c r="J613" s="42" t="n">
+        <x:f>B613-C613</x:f>
+        <x:v>-117.84</x:v>
+      </x:c>
+      <x:c r="K613" s="42" t="n">
+        <x:f>D613-F613</x:f>
+        <x:v>124.37000000000003</x:v>
+      </x:c>
+      <x:c r="L613" s="42" t="n">
+        <x:f>E613-G613</x:f>
+        <x:v>228.69</x:v>
+      </x:c>
+      <x:c r="M613" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N613" s="41" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" s="41" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B614" s="42" t="n">
+        <x:v>229.57</x:v>
+      </x:c>
+      <x:c r="C614" s="42" t="n">
+        <x:v>323.18</x:v>
+      </x:c>
+      <x:c r="D614" s="42" t="n">
+        <x:v>272.82</x:v>
+      </x:c>
+      <x:c r="E614" s="42" t="n">
+        <x:v>358.71</x:v>
+      </x:c>
+      <x:c r="F614" s="42" t="n">
+        <x:v>156.5</x:v>
+      </x:c>
+      <x:c r="G614" s="42" t="n">
+        <x:v>250.53</x:v>
+      </x:c>
+      <x:c r="H614" s="43" t="n">
+        <x:v>1801951.84</x:v>
+      </x:c>
+      <x:c r="I614" s="43" t="n">
+        <x:v>2040992.05</x:v>
+      </x:c>
+      <x:c r="J614" s="42" t="n">
+        <x:f>B614-C614</x:f>
+        <x:v>-93.61000000000001</x:v>
+      </x:c>
+      <x:c r="K614" s="42" t="n">
+        <x:f>D614-F614</x:f>
+        <x:v>116.32</x:v>
+      </x:c>
+      <x:c r="L614" s="42" t="n">
+        <x:f>E614-G614</x:f>
+        <x:v>108.17999999999998</x:v>
+      </x:c>
+      <x:c r="M614" s="29" t="str">
+        <x:v>网站结构化接口</x:v>
+      </x:c>
+      <x:c r="N614" s="41" t="n">
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -63685,8 +64014,442 @@
         <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508373&amp;idx=1&amp;sn=5775242f01351f95255fc9f692487e0a&amp;chksm=f9f9952fce8e1c39a0297087156ea17c215674d58075aa2b2cc1929653b3809fae91c95c45e3#rd</x:v>
       </x:c>
     </x:row>
+    <x:row r="608">
+      <x:c r="A608" s="41" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="B608" s="42" t="n">
+        <x:v>326.23</x:v>
+      </x:c>
+      <x:c r="C608" s="42" t="n">
+        <x:v>33.07</x:v>
+      </x:c>
+      <x:c r="D608" s="42" t="n">
+        <x:v>313.1</x:v>
+      </x:c>
+      <x:c r="E608" s="42" t="n">
+        <x:v>39.2</x:v>
+      </x:c>
+      <x:c r="F608" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G608" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H608" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I608" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J608" s="42" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="K608" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L608" s="42" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="M608" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N608" s="42" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="O608" s="42" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="P608" s="42" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="Q608" s="42" t="n">
+        <x:v>0.98</x:v>
+      </x:c>
+      <x:c r="R608" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S608" s="45" t="n">
+        <x:v>0.9624441862106323</x:v>
+      </x:c>
+      <x:c r="T608" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508377&amp;idx=1&amp;sn=0efbf8c8cbd15a7fbf69bffe0982da8e&amp;chksm=f9f99523ce8e1c3580af95a3a5cadff747dd6ea4e0a19d958c0d28338a1f0b7b8c034271605e#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609">
+      <x:c r="A609" s="41" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B609" s="42" t="n">
+        <x:v>318.57</x:v>
+      </x:c>
+      <x:c r="C609" s="42" t="n">
+        <x:v>35.24</x:v>
+      </x:c>
+      <x:c r="D609" s="42" t="n">
+        <x:v>243.75</x:v>
+      </x:c>
+      <x:c r="E609" s="42" t="n">
+        <x:v>34.77</x:v>
+      </x:c>
+      <x:c r="F609" s="42" t="n">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="G609" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H609" s="42" t="n">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="I609" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J609" s="42" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="K609" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L609" s="42" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="M609" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N609" s="42" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="O609" s="42" t="n">
+        <x:v>0.97</x:v>
+      </x:c>
+      <x:c r="P609" s="42" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="Q609" s="42" t="n">
+        <x:v>1.01</x:v>
+      </x:c>
+      <x:c r="R609" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S609" s="45" t="n">
+        <x:v>0.9999873638153076</x:v>
+      </x:c>
+      <x:c r="T609" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508383&amp;idx=1&amp;sn=878bc99506bdadd45fd0f585460c51ea&amp;chksm=f9f99525ce8e1c33b62ab2be5c9cdd71d62e485f8cf756989c4ab8cae6f4aa6a15eaccbc6c81#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610">
+      <x:c r="A610" s="41" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B610" s="42" t="n">
+        <x:v>299.88</x:v>
+      </x:c>
+      <x:c r="C610" s="42" t="n">
+        <x:v>39.95</x:v>
+      </x:c>
+      <x:c r="D610" s="42" t="n">
+        <x:v>263.98</x:v>
+      </x:c>
+      <x:c r="E610" s="42" t="n">
+        <x:v>32.19</x:v>
+      </x:c>
+      <x:c r="F610" s="42" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="G610" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H610" s="42" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="I610" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J610" s="42" t="n">
+        <x:v>454.03</x:v>
+      </x:c>
+      <x:c r="K610" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L610" s="42" t="n">
+        <x:v>454.03</x:v>
+      </x:c>
+      <x:c r="M610" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N610" s="42" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="O610" s="42" t="n">
+        <x:v>1.06</x:v>
+      </x:c>
+      <x:c r="P610" s="42" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="Q610" s="42" t="n">
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c r="R610" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S610" s="45" t="n">
+        <x:v>0.9999867677688599</x:v>
+      </x:c>
+      <x:c r="T610" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508388&amp;idx=1&amp;sn=4f88a54976d80acec48e56bf12b137bf&amp;chksm=f9f9951ece8e1c0880d2dfa4e6e865c9c4f8f9b6e26ba04dca3f908275b3e1af6769cfa6be3b#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611">
+      <x:c r="A611" s="41" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="B611" s="42" t="n">
+        <x:v>244.79</x:v>
+      </x:c>
+      <x:c r="C611" s="42" t="n">
+        <x:v>53.48</x:v>
+      </x:c>
+      <x:c r="D611" s="42" t="n">
+        <x:v>254.53</x:v>
+      </x:c>
+      <x:c r="E611" s="42" t="n">
+        <x:v>78.13</x:v>
+      </x:c>
+      <x:c r="F611" s="42" t="n">
+        <x:v>477.2</x:v>
+      </x:c>
+      <x:c r="G611" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H611" s="42" t="n">
+        <x:v>477.2</x:v>
+      </x:c>
+      <x:c r="I611" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J611" s="42" t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="K611" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L611" s="42" t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="M611" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N611" s="42" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="O611" s="42" t="n">
+        <x:v>1.06</x:v>
+      </x:c>
+      <x:c r="P611" s="42" t="n">
+        <x:v>0.87</x:v>
+      </x:c>
+      <x:c r="Q611" s="42" t="n">
+        <x:v>1.04</x:v>
+      </x:c>
+      <x:c r="R611" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S611" s="45" t="n">
+        <x:v>0.9999853372573853</x:v>
+      </x:c>
+      <x:c r="T611" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508393&amp;idx=1&amp;sn=2b031573351216aca13d298104133c4f&amp;chksm=f9f99513ce8e1c0516ec88e64a380791892c7875295409d5d674b8f57156af7ef0975ade9ed8#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612">
+      <x:c r="A612" s="41" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="B612" s="42" t="n">
+        <x:v>234.5</x:v>
+      </x:c>
+      <x:c r="C612" s="42" t="n">
+        <x:v>39.19</x:v>
+      </x:c>
+      <x:c r="D612" s="42" t="n">
+        <x:v>247.35</x:v>
+      </x:c>
+      <x:c r="E612" s="42" t="n">
+        <x:v>88.94</x:v>
+      </x:c>
+      <x:c r="F612" s="42" t="n">
+        <x:v>429.28</x:v>
+      </x:c>
+      <x:c r="G612" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H612" s="42" t="n">
+        <x:v>429.28</x:v>
+      </x:c>
+      <x:c r="I612" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J612" s="42" t="n">
+        <x:v>533.98</x:v>
+      </x:c>
+      <x:c r="K612" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L612" s="42" t="n">
+        <x:v>533.98</x:v>
+      </x:c>
+      <x:c r="M612" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N612" s="42" t="n">
+        <x:v>1.04</x:v>
+      </x:c>
+      <x:c r="O612" s="42" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="P612" s="42" t="n">
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c r="Q612" s="42" t="n">
+        <x:v>0.97</x:v>
+      </x:c>
+      <x:c r="R612" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S612" s="45" t="n">
+        <x:v>0.9999845027923584</x:v>
+      </x:c>
+      <x:c r="T612" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508409&amp;idx=1&amp;sn=7c34acacb099b7013d7a8e2ed957e3c1&amp;chksm=f9f99503ce8e1c15f4e1ba31bdf53629dd97ff6bb3667aa3819fe311ab2cb740e9b5518e4751#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613">
+      <x:c r="A613" s="41" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="B613" s="42" t="n">
+        <x:v>256.81</x:v>
+      </x:c>
+      <x:c r="C613" s="42" t="n">
+        <x:v>57.03</x:v>
+      </x:c>
+      <x:c r="D613" s="42" t="n">
+        <x:v>309.34</x:v>
+      </x:c>
+      <x:c r="E613" s="42" t="n">
+        <x:v>96.13</x:v>
+      </x:c>
+      <x:c r="F613" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G613" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H613" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I613" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J613" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="K613" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L613" s="42" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="M613" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N613" s="42" t="n">
+        <x:v>0.84</x:v>
+      </x:c>
+      <x:c r="O613" s="42" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="P613" s="42" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="Q613" s="42" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="R613" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S613" s="45" t="n">
+        <x:v>0.9999830722808838</x:v>
+      </x:c>
+      <x:c r="T613" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508419&amp;idx=1&amp;sn=f72c582b6aeb7d7f3215d2dc5707b98d&amp;chksm=f9f99579ce8e1c6f76c961b45fc3216eab613115aafa1a1099a7727f020bd5f16ed08db999aa#rd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" s="41" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B614" s="42" t="n">
+        <x:v>275.56</x:v>
+      </x:c>
+      <x:c r="C614" s="42" t="n">
+        <x:v>66.36</x:v>
+      </x:c>
+      <x:c r="D614" s="42" t="n">
+        <x:v>352.94</x:v>
+      </x:c>
+      <x:c r="E614" s="42" t="n">
+        <x:v>172.9</x:v>
+      </x:c>
+      <x:c r="F614" s="42" t="n">
+        <x:v>489.27</x:v>
+      </x:c>
+      <x:c r="G614" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H614" s="42" t="n">
+        <x:v>489.27</x:v>
+      </x:c>
+      <x:c r="I614" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J614" s="42" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="K614" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L614" s="42" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="M614" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N614" s="42" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="O614" s="42" t="n">
+        <x:v>0.97</x:v>
+      </x:c>
+      <x:c r="P614" s="42" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="Q614" s="42" t="n">
+        <x:v>0.99</x:v>
+      </x:c>
+      <x:c r="R614" s="29" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="S614" s="45" t="n">
+        <x:v>0.9998301863670349</x:v>
+      </x:c>
+      <x:c r="T614" s="29" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508423&amp;idx=1&amp;sn=d436a509a207125fb3fcd974e4c70723&amp;chksm=f9f9957dce8e1c6bcf8f7f6d3985f4f43e44c6f12c6bfb60a50f9be9177eae078e8a035a83c1#rd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="R2:R607">
+  <x:conditionalFormatting sqref="R2:R614">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>R2="ok"</x:formula>
     </x:cfRule>
@@ -63798,27 +64561,27 @@
         <x:v>45658</x:v>
       </x:c>
       <x:c r="B5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>329.55612903225807</x:v>
       </x:c>
       <x:c r="C5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>363.4670967741936</x:v>
       </x:c>
       <x:c r="D5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>351.32580645161295</x:v>
       </x:c>
       <x:c r="E5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>385.76935483870983</x:v>
       </x:c>
       <x:c r="F5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>215.62870967741932</x:v>
       </x:c>
       <x:c r="G5" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A5,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A5,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A5,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>246.1216129032258</x:v>
       </x:c>
       <x:c r="H5" s="39" t="n">
@@ -63831,27 +64594,27 @@
         <x:v>45689</x:v>
       </x:c>
       <x:c r="B6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>300.44928571428574</x:v>
       </x:c>
       <x:c r="C6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>260.71535714285716</x:v>
       </x:c>
       <x:c r="D6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>328.29571428571427</x:v>
       </x:c>
       <x:c r="E6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>279.91249999999997</x:v>
       </x:c>
       <x:c r="F6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>178.16428571428574</x:v>
       </x:c>
       <x:c r="G6" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A6,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A6,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A6,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>177.3103571428571</x:v>
       </x:c>
       <x:c r="H6" s="39" t="n">
@@ -63864,27 +64627,27 @@
         <x:v>45717</x:v>
       </x:c>
       <x:c r="B7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>279.8206451612903</x:v>
       </x:c>
       <x:c r="C7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>249.16709677419354</x:v>
       </x:c>
       <x:c r="D7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>312.7683870967742</x:v>
       </x:c>
       <x:c r="E7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>276.3945161290322</x:v>
       </x:c>
       <x:c r="F7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>171.45032258064512</x:v>
       </x:c>
       <x:c r="G7" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A7,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A7,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A7,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>160.2796774193548</x:v>
       </x:c>
       <x:c r="H7" s="39" t="n">
@@ -63897,27 +64660,27 @@
         <x:v>45748</x:v>
       </x:c>
       <x:c r="B8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>220.40933333333334</x:v>
       </x:c>
       <x:c r="C8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>227.9486666666667</x:v>
       </x:c>
       <x:c r="D8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>262.6410000000001</x:v>
       </x:c>
       <x:c r="E8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>269.39033333333333</x:v>
       </x:c>
       <x:c r="F8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>123.596</x:v>
       </x:c>
       <x:c r="G8" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A8,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A8,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A8,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>131.11266666666668</x:v>
       </x:c>
       <x:c r="H8" s="39" t="n">
@@ -63930,27 +64693,27 @@
         <x:v>45778</x:v>
       </x:c>
       <x:c r="B9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>216.26193548387099</x:v>
       </x:c>
       <x:c r="C9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>213.6558064516129</x:v>
       </x:c>
       <x:c r="D9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>249.0003225806452</x:v>
       </x:c>
       <x:c r="E9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>244.5761290322581</x:v>
       </x:c>
       <x:c r="F9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>131.72161290322578</x:v>
       </x:c>
       <x:c r="G9" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A9,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A9,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A9,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>132.73967741935485</x:v>
       </x:c>
       <x:c r="H9" s="39" t="n">
@@ -63963,27 +64726,27 @@
         <x:v>45809</x:v>
       </x:c>
       <x:c r="B10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>237.06566666666671</x:v>
       </x:c>
       <x:c r="C10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>242.62517241379314</x:v>
       </x:c>
       <x:c r="D10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>267.17533333333336</x:v>
       </x:c>
       <x:c r="E10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>266.20965517241376</x:v>
       </x:c>
       <x:c r="F10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>134.40133333333333</x:v>
       </x:c>
       <x:c r="G10" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A10,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A10,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A10,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>155.09344827586207</x:v>
       </x:c>
       <x:c r="H10" s="39" t="n">
@@ -63996,27 +64759,27 @@
         <x:v>45839</x:v>
       </x:c>
       <x:c r="B11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>251.60870967741943</x:v>
       </x:c>
       <x:c r="C11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>255.76096774193545</x:v>
       </x:c>
       <x:c r="D11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>281.05580645161297</x:v>
       </x:c>
       <x:c r="E11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>279.63709677419354</x:v>
       </x:c>
       <x:c r="F11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>136.8290322580645</x:v>
       </x:c>
       <x:c r="G11" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A11,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A11,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A11,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>157.16032258064516</x:v>
       </x:c>
       <x:c r="H11" s="39" t="n">
@@ -64029,27 +64792,27 @@
         <x:v>45870</x:v>
       </x:c>
       <x:c r="B12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>298.37354838709683</x:v>
       </x:c>
       <x:c r="C12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>295.5012903225807</x:v>
       </x:c>
       <x:c r="D12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>332.4093548387097</x:v>
       </x:c>
       <x:c r="E12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>323.1909677419355</x:v>
       </x:c>
       <x:c r="F12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>151.3493548387097</x:v>
       </x:c>
       <x:c r="G12" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A12,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A12,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A12,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>169.80516129032256</x:v>
       </x:c>
       <x:c r="H12" s="39" t="n">
@@ -64062,27 +64825,27 @@
         <x:v>45901</x:v>
       </x:c>
       <x:c r="B13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>144.22233333333335</x:v>
       </x:c>
       <x:c r="C13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>200.23433333333338</x:v>
       </x:c>
       <x:c r="D13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>164.3046666666666</x:v>
       </x:c>
       <x:c r="E13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>218.50633333333334</x:v>
       </x:c>
       <x:c r="F13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>95.92533333333337</x:v>
       </x:c>
       <x:c r="G13" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A13,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A13,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A13,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>152.36366666666666</x:v>
       </x:c>
       <x:c r="H13" s="39" t="n">
@@ -64095,27 +64858,27 @@
         <x:v>45931</x:v>
       </x:c>
       <x:c r="B14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>257.27516129032256</x:v>
       </x:c>
       <x:c r="C14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>319.4687096774194</x:v>
       </x:c>
       <x:c r="D14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>279.0945161290323</x:v>
       </x:c>
       <x:c r="E14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>340.140322580645</x:v>
       </x:c>
       <x:c r="F14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>171.19580645161287</x:v>
       </x:c>
       <x:c r="G14" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A14,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A14,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A14,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>228.87322580645167</x:v>
       </x:c>
       <x:c r="H14" s="39" t="n">
@@ -64128,27 +64891,27 @@
         <x:v>45962</x:v>
       </x:c>
       <x:c r="B15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>187.08299999999994</x:v>
       </x:c>
       <x:c r="C15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>208.76566666666668</x:v>
       </x:c>
       <x:c r="D15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>208.34633333333332</x:v>
       </x:c>
       <x:c r="E15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>231.30599999999998</x:v>
       </x:c>
       <x:c r="F15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>103.11566666666664</x:v>
       </x:c>
       <x:c r="G15" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A15,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A15,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A15,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>115.58999999999999</x:v>
       </x:c>
       <x:c r="H15" s="39" t="n">
@@ -64161,27 +64924,27 @@
         <x:v>45992</x:v>
       </x:c>
       <x:c r="B16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>271.9325806451613</x:v>
       </x:c>
       <x:c r="C16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>273.27806451612906</x:v>
       </x:c>
       <x:c r="D16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>299.0351612903226</x:v>
       </x:c>
       <x:c r="E16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>299.65322580645164</x:v>
       </x:c>
       <x:c r="F16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>140.0470967741936</x:v>
       </x:c>
       <x:c r="G16" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A16,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A16,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A16,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>139.21290322580646</x:v>
       </x:c>
       <x:c r="H16" s="39" t="n">
@@ -64194,27 +64957,27 @@
         <x:v>46023</x:v>
       </x:c>
       <x:c r="B17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>279.0032258064516</x:v>
       </x:c>
       <x:c r="C17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>271.9425806451613</x:v>
       </x:c>
       <x:c r="D17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>300.0367741935484</x:v>
       </x:c>
       <x:c r="E17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>289.38000000000005</x:v>
       </x:c>
       <x:c r="F17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>180.67709677419356</x:v>
       </x:c>
       <x:c r="G17" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A17,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A17,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A17,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>186.3467741935484</x:v>
       </x:c>
       <x:c r="H17" s="39" t="n">
@@ -64227,27 +64990,27 @@
         <x:v>46054</x:v>
       </x:c>
       <x:c r="B18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>208.5582142857143</x:v>
       </x:c>
       <x:c r="C18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>199.73857142857145</x:v>
       </x:c>
       <x:c r="D18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>238.7057142857143</x:v>
       </x:c>
       <x:c r="E18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>225.0778571428571</x:v>
       </x:c>
       <x:c r="F18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>98.31035714285713</x:v>
       </x:c>
       <x:c r="G18" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A18,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A18,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A18,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>103.44857142857143</x:v>
       </x:c>
       <x:c r="H18" s="39" t="n">
@@ -64260,27 +65023,27 @@
         <x:v>46082</x:v>
       </x:c>
       <x:c r="B19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>214.751935483871</x:v>
       </x:c>
       <x:c r="C19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>210.5164516129032</x:v>
       </x:c>
       <x:c r="D19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>245.5132258064516</x:v>
       </x:c>
       <x:c r="E19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>237.59838709677413</x:v>
       </x:c>
       <x:c r="F19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>123.60064516129032</x:v>
       </x:c>
       <x:c r="G19" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A19,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A19,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A19,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>129.11387096774195</x:v>
       </x:c>
       <x:c r="H19" s="39" t="n">
@@ -64293,27 +65056,27 @@
         <x:v>46113</x:v>
       </x:c>
       <x:c r="B20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>159.10166666666666</x:v>
       </x:c>
       <x:c r="C20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>159.5346666666667</x:v>
       </x:c>
       <x:c r="D20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>204.07900000000004</x:v>
       </x:c>
       <x:c r="E20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>199.92633333333336</x:v>
       </x:c>
       <x:c r="F20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>77.90900000000002</x:v>
       </x:c>
       <x:c r="G20" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A20,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A20,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A20,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>85.97333333333333</x:v>
       </x:c>
       <x:c r="H20" s="39" t="n">
@@ -64326,27 +65089,27 @@
         <x:v>46143</x:v>
       </x:c>
       <x:c r="B21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>143.0783870967742</x:v>
       </x:c>
       <x:c r="C21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>149.3541935483871</x:v>
       </x:c>
       <x:c r="D21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>175.76451612903227</x:v>
       </x:c>
       <x:c r="E21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>185.0235483870968</x:v>
       </x:c>
       <x:c r="F21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>72.17032258064515</x:v>
       </x:c>
       <x:c r="G21" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A21,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A21,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A21,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>72.60258064516127</x:v>
       </x:c>
       <x:c r="H21" s="39" t="n">
@@ -64359,27 +65122,27 @@
         <x:v>46174</x:v>
       </x:c>
       <x:c r="B22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>178.90266666666665</x:v>
       </x:c>
       <x:c r="C22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>174.07900000000006</x:v>
       </x:c>
       <x:c r="D22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>216.8056666666667</x:v>
       </x:c>
       <x:c r="E22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>211.91700000000003</x:v>
       </x:c>
       <x:c r="F22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>99.698</x:v>
       </x:c>
       <x:c r="G22" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A22,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A22,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A22,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>96.31866666666669</x:v>
       </x:c>
       <x:c r="H22" s="39" t="n">
@@ -64392,27 +65155,27 @@
         <x:v>46204</x:v>
       </x:c>
       <x:c r="B23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
         <x:v>291.8641935483871</x:v>
       </x:c>
       <x:c r="C23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
         <x:v>293.24677419354845</x:v>
       </x:c>
       <x:c r="D23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
         <x:v>317.33600000000007</x:v>
       </x:c>
       <x:c r="E23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
         <x:v>317.49</x:v>
       </x:c>
       <x:c r="F23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
         <x:v>199.67500000000004</x:v>
       </x:c>
       <x:c r="G23" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A23,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A23,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A23,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
         <x:v>204.3896666666666</x:v>
       </x:c>
       <x:c r="H23" s="39" t="n">
@@ -64425,32 +65188,65 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$B$2:$B$607,"&lt;&gt;"),"")</x:f>
-        <x:v>228.57000000000002</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
+        <x:v>229.97129032258067</x:v>
       </x:c>
       <x:c r="C24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$C$2:$C$607,"&lt;&gt;"),"")</x:f>
-        <x:v>239.42896551724132</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
+        <x:v>238.56258064516126</x:v>
       </x:c>
       <x:c r="D24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$D$2:$D$607,"&lt;&gt;"),"")</x:f>
-        <x:v>252.32310344827584</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
+        <x:v>255.03387096774193</x:v>
       </x:c>
       <x:c r="E24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$E$2:$E$607,"&lt;&gt;"),"")</x:f>
-        <x:v>264.34379310344826</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
+        <x:v>264.5206451612903</x:v>
       </x:c>
       <x:c r="F24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$F$2:$F$607,"&lt;&gt;"),"")</x:f>
-        <x:v>146.85172413793103</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
+        <x:v>142.32258064516125</x:v>
       </x:c>
       <x:c r="G24" s="39" t="n">
-        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$607,'每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$607,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$607,"&lt;"&amp;EDATE($A24,1),'每日数据'!$G$2:$G$607,"&lt;&gt;"),"")</x:f>
-        <x:v>153.83965517241379</x:v>
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A24,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A24,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
+        <x:v>148.70322580645163</x:v>
       </x:c>
       <x:c r="H24" s="39" t="n">
         <x:f>B24-C24</x:f>
-        <x:v>-10.858965517241302</x:v>
+        <x:v>-8.59129032258059</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="46" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B25" s="39" t="n">
+        <x:f>IFERROR(SUMIFS('每日数据'!$B$2:$B$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1),'每日数据'!$B$2:$B$614,"&lt;&gt;"),"")</x:f>
+        <x:v>224.83200000000002</x:v>
+      </x:c>
+      <x:c r="C25" s="39" t="n">
+        <x:f>IFERROR(SUMIFS('每日数据'!$C$2:$C$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1),'每日数据'!$C$2:$C$614,"&lt;&gt;"),"")</x:f>
+        <x:v>266.258</x:v>
+      </x:c>
+      <x:c r="D25" s="39" t="n">
+        <x:f>IFERROR(SUMIFS('每日数据'!$D$2:$D$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1),'每日数据'!$D$2:$D$614,"&lt;&gt;"),"")</x:f>
+        <x:v>271.348</x:v>
+      </x:c>
+      <x:c r="E25" s="39" t="n">
+        <x:f>IFERROR(SUMIFS('每日数据'!$E$2:$E$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1),'每日数据'!$E$2:$E$614,"&lt;&gt;"),"")</x:f>
+        <x:v>313.446</x:v>
+      </x:c>
+      <x:c r="F25" s="39" t="n">
+        <x:f>IFERROR(SUMIFS('每日数据'!$F$2:$F$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1),'每日数据'!$F$2:$F$614,"&lt;&gt;"),"")</x:f>
+        <x:v>142.82999999999998</x:v>
+      </x:c>
+      <x:c r="G25" s="39" t="n">
+        <x:f>IFERROR(SUMIFS('每日数据'!$G$2:$G$614,'每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1))/COUNTIFS('每日数据'!$A$2:$A$614,"&gt;="&amp;$A25,'每日数据'!$A$2:$A$614,"&lt;"&amp;EDATE($A25,1),'每日数据'!$G$2:$G$614,"&lt;&gt;"),"")</x:f>
+        <x:v>179.36399999999998</x:v>
+      </x:c>
+      <x:c r="H25" s="39" t="n">
+        <x:f>B25-C25</x:f>
+        <x:v>-41.42599999999996</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -65053,27 +65849,57 @@
       </x:c>
       <x:c r="B60" t="n">
         <x:f>B24</x:f>
-        <x:v>228.57000000000002</x:v>
+        <x:v>229.97129032258067</x:v>
       </x:c>
       <x:c r="C60" t="n">
         <x:f>C24</x:f>
-        <x:v>239.42896551724132</x:v>
+        <x:v>238.56258064516126</x:v>
       </x:c>
       <x:c r="D60" t="n">
         <x:f>D24</x:f>
-        <x:v>252.32310344827584</x:v>
+        <x:v>255.03387096774193</x:v>
       </x:c>
       <x:c r="E60" t="n">
         <x:f>E24</x:f>
-        <x:v>264.34379310344826</x:v>
+        <x:v>264.5206451612903</x:v>
       </x:c>
       <x:c r="F60" t="n">
         <x:f>F24</x:f>
-        <x:v>146.85172413793103</x:v>
+        <x:v>142.32258064516125</x:v>
       </x:c>
       <x:c r="G60" t="n">
         <x:f>G24</x:f>
-        <x:v>153.83965517241379</x:v>
+        <x:v>148.70322580645163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:f>TEXT(A25,"yyyy-mm")</x:f>
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B61" t="n">
+        <x:f>B25</x:f>
+        <x:v>224.83200000000002</x:v>
+      </x:c>
+      <x:c r="C61" t="n">
+        <x:f>C25</x:f>
+        <x:v>266.258</x:v>
+      </x:c>
+      <x:c r="D61" t="n">
+        <x:f>D25</x:f>
+        <x:v>271.348</x:v>
+      </x:c>
+      <x:c r="E61" t="n">
+        <x:f>E25</x:f>
+        <x:v>313.446</x:v>
+      </x:c>
+      <x:c r="F61" t="n">
+        <x:f>F25</x:f>
+        <x:v>142.82999999999998</x:v>
+      </x:c>
+      <x:c r="G61" t="n">
+        <x:f>G25</x:f>
+        <x:v>179.36399999999998</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -65082,7 +65908,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9baa7fcae0e4d86"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf796ed610bb44bc6"/>
 </x:worksheet>
 </file>
 
@@ -65640,24 +66466,49 @@
         <x:v>46235</x:v>
       </x:c>
       <x:c r="B24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$B$579:$B$607)</x:f>
-        <x:v>235.1403703703704</x:v>
+        <x:f>AVERAGE('风光分项'!$B$579:$B$609)</x:f>
+        <x:v>241.15827586206896</x:v>
       </x:c>
       <x:c r="C24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$C$579:$C$607)</x:f>
-        <x:v>106.69259259259259</x:v>
+        <x:f>AVERAGE('风光分项'!$C$579:$C$609)</x:f>
+        <x:v>101.69</x:v>
       </x:c>
       <x:c r="D24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$D$579:$D$607)</x:f>
-        <x:v>227.18703703703704</x:v>
+        <x:f>AVERAGE('风光分项'!$D$579:$D$609)</x:f>
+        <x:v>230.72068965517244</x:v>
       </x:c>
       <x:c r="E24" s="52" t="n">
-        <x:f>AVERAGE('风光分项'!$E$579:$E$607)</x:f>
-        <x:v>110.82629629629629</x:v>
+        <x:f>AVERAGE('风光分项'!$E$579:$E$609)</x:f>
+        <x:v>105.73379310344826</x:v>
       </x:c>
       <x:c r="F24" s="53" t="n">
-        <x:f>COUNT('风光分项'!$B$579:$B$607)</x:f>
-        <x:v>27</x:v>
+        <x:f>COUNT('风光分项'!$B$579:$B$609)</x:f>
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="51" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B25" s="52" t="n">
+        <x:f>AVERAGE('风光分项'!$B$610:$B$614)</x:f>
+        <x:v>262.308</x:v>
+      </x:c>
+      <x:c r="C25" s="52" t="n">
+        <x:f>AVERAGE('风光分项'!$C$610:$C$614)</x:f>
+        <x:v>51.202</x:v>
+      </x:c>
+      <x:c r="D25" s="52" t="n">
+        <x:f>AVERAGE('风光分项'!$D$610:$D$614)</x:f>
+        <x:v>285.62800000000004</x:v>
+      </x:c>
+      <x:c r="E25" s="52" t="n">
+        <x:f>AVERAGE('风光分项'!$E$610:$E$614)</x:f>
+        <x:v>93.65799999999999</x:v>
+      </x:c>
+      <x:c r="F25" s="53" t="n">
+        <x:f>COUNT('风光分项'!$B$610:$B$614)</x:f>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -66036,19 +66887,41 @@
       </x:c>
       <x:c r="B57" t="n">
         <x:f>B24</x:f>
-        <x:v>235.1403703703704</x:v>
+        <x:v>241.15827586206896</x:v>
       </x:c>
       <x:c r="C57" t="n">
         <x:f>C24</x:f>
-        <x:v>106.69259259259259</x:v>
+        <x:v>101.69</x:v>
       </x:c>
       <x:c r="D57" t="n">
         <x:f>D24</x:f>
-        <x:v>227.18703703703704</x:v>
+        <x:v>230.72068965517244</x:v>
       </x:c>
       <x:c r="E57" t="n">
         <x:f>E24</x:f>
-        <x:v>110.82629629629629</x:v>
+        <x:v>105.73379310344826</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:f>TEXT(A25,"yyyy-mm")</x:f>
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="B58" t="n">
+        <x:f>B25</x:f>
+        <x:v>262.308</x:v>
+      </x:c>
+      <x:c r="C58" t="n">
+        <x:f>C25</x:f>
+        <x:v>51.202</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:f>D25</x:f>
+        <x:v>285.62800000000004</x:v>
+      </x:c>
+      <x:c r="E58" t="n">
+        <x:f>E25</x:f>
+        <x:v>93.65799999999999</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -66057,7 +66930,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61d1092449c43ef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc5cff6f9dc94a9a"/>
 </x:worksheet>
 </file>
 
@@ -66099,28 +66972,28 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>检查范围：2025-01-01 至 2026-08-29；同一自然日一行，共 606 行。</x:v>
+        <x:v>检查范围：2025-01-01 至 2026-09-05；同一自然日一行，共 613 行。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -66151,11 +67024,11 @@
         <x:v>日期行数</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:f>COUNTA('每日数据'!$A$2:$A$607)</x:f>
-        <x:v>606</x:v>
+        <x:f>COUNTA('每日数据'!$A$2:$A$614)</x:f>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="C5" s="14" t="n">
-        <x:v>606</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="D5" s="14" t="n">
         <x:f>B5-C5</x:f>
@@ -66177,7 +67050,7 @@
         <x:v>最早日期</x:v>
       </x:c>
       <x:c r="B6" s="15" t="n">
-        <x:f>MIN('每日数据'!$A$2:$A$607)</x:f>
+        <x:f>MIN('每日数据'!$A$2:$A$614)</x:f>
         <x:v>45658</x:v>
       </x:c>
       <x:c r="C6" s="15" t="n">
@@ -66203,11 +67076,11 @@
         <x:v>最晚日期</x:v>
       </x:c>
       <x:c r="B7" s="15" t="n">
-        <x:f>MAX('每日数据'!$A$2:$A$607)</x:f>
-        <x:v>46263</x:v>
+        <x:f>MAX('每日数据'!$A$2:$A$614)</x:f>
+        <x:v>46270</x:v>
       </x:c>
       <x:c r="C7" s="15" t="n">
-        <x:v>46263</x:v>
+        <x:v>46270</x:v>
       </x:c>
       <x:c r="D7" s="57" t="n">
         <x:f>B7-C7</x:f>
@@ -66229,11 +67102,11 @@
         <x:v>六类价格完整数</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:f>COUNT('每日数据'!$B$2:$G$607)</x:f>
-        <x:v>3629</x:v>
+        <x:f>COUNT('每日数据'!$B$2:$G$614)</x:f>
+        <x:v>3671</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>3629</x:v>
+        <x:v>3671</x:v>
       </x:c>
       <x:c r="D8" s="14" t="n">
         <x:f>B8-C8</x:f>
@@ -66247,7 +67120,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>理论3636；源站已知空值7个，保留为空</x:v>
+        <x:v>理论3678；源站已知空值7个，保留为空</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -66255,11 +67128,11 @@
         <x:v>总体电量完整数</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:f>COUNT('每日数据'!$H$2:$I$607)</x:f>
-        <x:v>1212</x:v>
+        <x:f>COUNT('每日数据'!$H$2:$I$614)</x:f>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="C9" s="14" t="n">
-        <x:v>1212</x:v>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="D9" s="14" t="n">
         <x:f>B9-C9</x:f>
@@ -66273,7 +67146,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>理论1212；源站已知空值0个，保留为空</x:v>
+        <x:v>理论1226；源站已知空值0个，保留为空</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
@@ -66281,7 +67154,7 @@
         <x:v>重复日期数</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
-        <x:f>SUMPRODUCT(--(COUNTIF('每日数据'!$A$2:$A$607,'每日数据'!$A$2:$A$607)&gt;1))</x:f>
+        <x:f>SUMPRODUCT(--(COUNTIF('每日数据'!$A$2:$A$614,'每日数据'!$A$2:$A$614)&gt;1))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="14" t="n">
@@ -66307,11 +67180,11 @@
         <x:v>风光四类均价完整数</x:v>
       </x:c>
       <x:c r="B11" s="14" t="n">
-        <x:f>COUNT('风光分项'!$B$2:$E$607)</x:f>
-        <x:v>2032</x:v>
+        <x:f>COUNT('风光分项'!$B$2:$E$614)</x:f>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="C11" s="14" t="n">
-        <x:v>2032</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="D11" s="14" t="n">
         <x:f>B11-C11</x:f>
@@ -66325,7 +67198,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>508个披露日×4列</x:v>
+        <x:v>515个披露日×4列</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
@@ -66333,7 +67206,7 @@
         <x:v>风光OCR待复核数</x:v>
       </x:c>
       <x:c r="B12" s="14" t="n">
-        <x:f>COUNTIF('风光分项'!$R$2:$R$607,"ocr_review")+COUNTIF('风光分项'!$R$2:$R$607,"range_review")+COUNTIF('风光分项'!$R$2:$R$607,"confidence_review")+COUNTIF('风光分项'!$R$2:$R$607,"待复核")</x:f>
+        <x:f>COUNTIF('风光分项'!$R$2:$R$614,"ocr_review")+COUNTIF('风光分项'!$R$2:$R$614,"range_review")+COUNTIF('风光分项'!$R$2:$R$614,"confidence_review")+COUNTIF('风光分项'!$R$2:$R$614,"待复核")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="14" t="n">
@@ -66405,7 +67278,7 @@
         <x:v>公众号与网站差异</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>2026-08-29两来源价格或电量存在口径差异</x:v>
+        <x:v>2026-09-05两来源价格或电量存在口径差异</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
         <x:v>同日数值不可直接混合</x:v>
@@ -66625,7 +67498,7 @@
         <x:v>主数据源</x:v>
       </x:c>
       <x:c r="G6" s="15" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str">
         <x:v>公开结构化接口，每次返回近15日</x:v>
@@ -66651,10 +67524,10 @@
         <x:v>发布快照/交叉核验</x:v>
       </x:c>
       <x:c r="G7" s="15" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>已抓取508个风光分项披露日；部分明细为图片</x:v>
+        <x:v>已抓取515个风光分项披露日；部分明细为图片</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -66662,10 +67535,10 @@
         <x:v>S3</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>公众号-2026-08-29日报</x:v>
+        <x:v>公众号-2026-09-05日报</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508373&amp;idx=1&amp;sn=5775242f01351f95255fc9f692487e0a&amp;chksm=f9f9952fce8e1c39a0297087156ea17c215674d58075aa2b2cc1929653b3809fae91c95c45e3#rd</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzUxOTMxNjk0OQ==&amp;mid=2247508423&amp;idx=1&amp;sn=d436a509a207125fb3fcd974e4c70723&amp;chksm=f9f9957dce8e1c6bcf8f7f6d3985f4f43e44c6f12c6bfb60a50f9be9177eae078e8a035a83c1#rd</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
         <x:v>差异核验样本</x:v>
@@ -66677,10 +67550,10 @@
         <x:v>证据样本</x:v>
       </x:c>
       <x:c r="G8" s="15" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str">
-        <x:v>日前172.48、实时188.04元/MWh</x:v>
+        <x:v>日前229.57、实时323.18元/MWh</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -66703,7 +67576,7 @@
         <x:v>风光分项主数据源</x:v>
       </x:c>
       <x:c r="G9" s="15" t="n">
-        <x:v>46265</x:v>
+        <x:v>46272</x:v>
       </x:c>
       <x:c r="H9" s="14" t="str">
         <x:v>2025-04-06起披露；OCR提取，逐行保留原文链接与置信度</x:v>
@@ -67086,6 +67959,6 @@
     <x:mergeCell ref="A21:H21"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e7f27ffb6554db0"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb878597868e74aa1"/>
 </x:worksheet>
 </file>